--- a/FFT Scoring Log.xlsx
+++ b/FFT Scoring Log.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siripes\Desktop\FFT ranking\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siripes\Desktop\FFT_Ranking_Dashboard_Full_V1_1_FIXED\FFT_Ranking_Full_V1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="95">
   <si>
     <t>Year</t>
   </si>
@@ -371,12 +371,6 @@
   </si>
   <si>
     <t>Security</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>July</t>
   </si>
 </sst>
 </file>
@@ -854,10 +848,10 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="9" width="12" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="14" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -928,7 +922,7 @@
       </c>
       <c r="K2" s="4">
         <f>IF(J2="","",1+COUNTIFS($A$2:$A$501,A2,$B$2:$B$501,B2,$J$2:$J$501,"&gt;"&amp;J2))</f>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -967,7 +961,7 @@
       </c>
       <c r="K3" s="4">
         <f t="shared" ref="K3:K65" si="3">IF(J3="","",1+COUNTIFS($A$2:$A$501,A3,$B$2:$B$501,B3,$J$2:$J$501,"&gt;"&amp;J3))</f>
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -986,27 +980,23 @@
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2">
-        <v>51</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1041,7 +1031,7 @@
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1080,7 +1070,7 @@
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1115,7 +1105,7 @@
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1173,27 +1163,23 @@
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="2">
-        <v>16</v>
-      </c>
-      <c r="G9" s="2">
-        <v>49</v>
-      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
       <c r="H9" s="3">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="1"/>
-        <v>18.329999999999998</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="2"/>
-        <v>58.33</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1228,7 +1214,7 @@
       </c>
       <c r="K10" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1267,7 +1253,7 @@
       </c>
       <c r="K11" s="4">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1302,7 +1288,7 @@
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1341,7 +1327,7 @@
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1376,7 +1362,7 @@
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1395,27 +1381,23 @@
       <c r="E15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="2">
-        <v>17</v>
-      </c>
-      <c r="G15" s="2">
-        <v>60</v>
-      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>43.5</v>
+        <v>0</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1450,7 +1432,7 @@
       </c>
       <c r="K16" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1489,7 +1471,7 @@
       </c>
       <c r="K17" s="4">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1524,7 +1506,7 @@
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1543,23 +1525,19 @@
       <c r="E19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="2">
-        <v>17</v>
-      </c>
-      <c r="G19" s="2">
-        <v>52</v>
-      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
       <c r="H19" s="3">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="1"/>
-        <v>13.33</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>55.83</v>
+        <v>0</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
@@ -1598,7 +1576,7 @@
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1617,27 +1595,23 @@
       <c r="E21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="2">
-        <v>14</v>
-      </c>
-      <c r="G21" s="2">
-        <v>59</v>
-      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
       <c r="H21" s="3">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="1"/>
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>36.67</v>
+        <v>0</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1672,7 +1646,7 @@
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1711,7 +1685,7 @@
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1730,27 +1704,23 @@
       <c r="E24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="2">
-        <v>14</v>
-      </c>
-      <c r="G24" s="2">
-        <v>57</v>
-      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
       <c r="H24" s="3">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1769,27 +1739,23 @@
       <c r="E25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="2">
-        <v>15</v>
-      </c>
-      <c r="G25" s="2">
-        <v>51</v>
-      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
       <c r="H25" s="3">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3">
         <f t="shared" si="4"/>
-        <v>52.5</v>
+        <v>0</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1824,7 +1790,7 @@
       </c>
       <c r="K26" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1843,27 +1809,23 @@
       <c r="E27" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="2">
-        <v>15</v>
-      </c>
-      <c r="G27" s="2">
-        <v>59</v>
-      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
       <c r="H27" s="3">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="1"/>
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
         <f t="shared" si="4"/>
-        <v>39.17</v>
+        <v>0</v>
       </c>
       <c r="K27" s="4">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1882,27 +1844,23 @@
       <c r="E28" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="2">
-        <v>18</v>
-      </c>
-      <c r="G28" s="2">
-        <v>55</v>
-      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
       <c r="H28" s="3">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="1"/>
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3">
         <f t="shared" si="4"/>
-        <v>53.33</v>
+        <v>0</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1921,27 +1879,23 @@
       <c r="E29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="2">
-        <v>16</v>
-      </c>
-      <c r="G29" s="2">
-        <v>50</v>
-      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
       <c r="H29" s="3">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="1"/>
-        <v>16.670000000000002</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <f t="shared" si="4"/>
-        <v>56.67</v>
+        <v>0</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1960,27 +1914,23 @@
       <c r="E30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="2">
-        <v>17</v>
-      </c>
-      <c r="G30" s="2">
-        <v>50</v>
-      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
       <c r="H30" s="3">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" si="1"/>
-        <v>16.670000000000002</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" si="4"/>
-        <v>59.17</v>
+        <v>0</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2015,7 +1965,7 @@
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2050,7 +2000,7 @@
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2085,7 +2035,7 @@
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -2120,7 +2070,7 @@
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2155,7 +2105,7 @@
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -2190,7 +2140,7 @@
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2225,7 +2175,7 @@
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2244,27 +2194,23 @@
       <c r="E38" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F38" s="2">
-        <v>12</v>
-      </c>
-      <c r="G38" s="2">
-        <v>50</v>
-      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
       <c r="H38" s="3">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I38" s="3">
         <f t="shared" si="1"/>
-        <v>16.670000000000002</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3">
         <f t="shared" si="4"/>
-        <v>46.67</v>
+        <v>0</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2283,27 +2229,23 @@
       <c r="E39" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F39" s="2">
-        <v>16</v>
-      </c>
-      <c r="G39" s="2">
-        <v>47</v>
-      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
       <c r="H39" s="3">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3">
         <f t="shared" si="1"/>
-        <v>21.67</v>
+        <v>0</v>
       </c>
       <c r="J39" s="3">
         <f t="shared" si="4"/>
-        <v>61.67</v>
+        <v>0</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2322,27 +2264,23 @@
       <c r="E40" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F40" s="2">
-        <v>16</v>
-      </c>
-      <c r="G40" s="2">
-        <v>45</v>
-      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
       <c r="H40" s="3">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3">
         <f t="shared" si="4"/>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K40" s="4">
         <f>IF(J40="","",1+COUNTIFS($A$2:$A$501,A40,$B$2:$B$501,B40,$J$2:$J$501,"&gt;"&amp;J40))</f>
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2361,27 +2299,23 @@
       <c r="E41" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F41" s="2">
-        <v>17</v>
-      </c>
-      <c r="G41" s="2">
-        <v>48</v>
-      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
       <c r="H41" s="3">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3">
         <f t="shared" si="4"/>
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="K41" s="4">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2416,7 +2350,7 @@
       </c>
       <c r="K42" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2435,27 +2369,23 @@
       <c r="E43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F43" s="2">
-        <v>18</v>
-      </c>
-      <c r="G43" s="2">
-        <v>55</v>
-      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
       <c r="H43" s="3">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
         <f t="shared" si="1"/>
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3">
         <f t="shared" si="4"/>
-        <v>53.33</v>
+        <v>0</v>
       </c>
       <c r="K43" s="4">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2490,7 +2420,7 @@
       </c>
       <c r="K44" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2525,7 +2455,7 @@
       </c>
       <c r="K45" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2560,7 +2490,7 @@
       </c>
       <c r="K46" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2595,7 +2525,7 @@
       </c>
       <c r="K47" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2630,7 +2560,7 @@
       </c>
       <c r="K48" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2665,7 +2595,7 @@
       </c>
       <c r="K49" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2700,7 +2630,7 @@
       </c>
       <c r="K50" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2735,7 +2665,7 @@
       </c>
       <c r="K51" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2770,7 +2700,7 @@
       </c>
       <c r="K52" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2805,7 +2735,7 @@
       </c>
       <c r="K53" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2840,7 +2770,7 @@
       </c>
       <c r="K54" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2875,7 +2805,7 @@
       </c>
       <c r="K55" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2910,7 +2840,7 @@
       </c>
       <c r="K56" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2945,7 +2875,7 @@
       </c>
       <c r="K57" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2980,7 +2910,7 @@
       </c>
       <c r="K58" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -3015,7 +2945,7 @@
       </c>
       <c r="K59" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -3052,7 +2982,7 @@
       </c>
       <c r="K60" s="4">
         <f>IF(J60="","",1+COUNTIFS($A$2:$A$501,A60,$B$2:$B$501,B60,$J$2:$J$501,"&gt;"&amp;J60))</f>
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -3087,7 +3017,7 @@
       </c>
       <c r="K61" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -3122,7 +3052,7 @@
       </c>
       <c r="K62" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -3157,7 +3087,7 @@
       </c>
       <c r="K63" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -3192,1061 +3122,715 @@
       </c>
       <c r="K64" s="4">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" s="8">
-        <v>100183</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F65" s="2">
-        <v>18</v>
-      </c>
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="3">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I65" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J65" s="3">
+      <c r="J65" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="K65" s="4">
+        <v/>
+      </c>
+      <c r="K65" s="4" t="str">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C66" s="8">
-        <v>100206</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F66" s="2">
-        <v>20</v>
-      </c>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="3">
         <f t="shared" ref="H66:H129" si="5">IF(OR(F66="",F66=0),0,ROUND((F66/20)*50,2))</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I66" s="3">
         <f t="shared" ref="I66:I129" si="6">IF(OR(G66="",G66=0),0,ROUND(IF(G66&lt;=30,50,IF(G66&gt;=60,1,50-((G66-30)*(50/30)))),2))</f>
         <v>0</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="K66" s="4">
+        <v/>
+      </c>
+      <c r="K66" s="4" t="str">
         <f t="shared" ref="K66:K129" si="7">IF(J66="","",1+COUNTIFS($A$2:$A$501,A66,$B$2:$B$501,B66,$J$2:$J$501,"&gt;"&amp;J66))</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C67" s="8">
-        <v>100142</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="2">
-        <v>20</v>
-      </c>
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I67" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J67" s="3">
+      <c r="J67" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="K67" s="4">
+        <v/>
+      </c>
+      <c r="K67" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C68" s="8">
-        <v>100479</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F68" s="2">
-        <v>19</v>
-      </c>
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I68" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J68" s="3">
+      <c r="J68" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>47.5</v>
-      </c>
-      <c r="K68" s="4">
+        <v/>
+      </c>
+      <c r="K68" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C69" s="8">
-        <v>100498</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F69" s="2">
-        <v>18</v>
-      </c>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I69" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J69" s="3">
+      <c r="J69" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="K69" s="4">
+        <v/>
+      </c>
+      <c r="K69" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C70" s="8">
-        <v>100140</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70" s="2">
-        <v>17</v>
-      </c>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="3">
         <f t="shared" si="5"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J70" s="3">
+      <c r="J70" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>42.5</v>
-      </c>
-      <c r="K70" s="4">
+        <v/>
+      </c>
+      <c r="K70" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>51</v>
+        <v/>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C71" s="8">
-        <v>100324</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F71" s="2">
-        <v>20</v>
-      </c>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I71" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J71" s="3">
+      <c r="J71" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="K71" s="4">
+        <v/>
+      </c>
+      <c r="K71" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72" s="8">
-        <v>100413</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F72" s="2">
-        <v>19</v>
-      </c>
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I72" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>47.5</v>
-      </c>
-      <c r="K72" s="4">
+        <v/>
+      </c>
+      <c r="K72" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C73" s="8">
-        <v>100577</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="2">
-        <v>20</v>
-      </c>
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I73" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J73" s="3">
+      <c r="J73" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="K73" s="4">
+        <v/>
+      </c>
+      <c r="K73" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C74" s="8">
-        <v>100642</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" s="2">
-        <v>20</v>
-      </c>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I74" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J74" s="3">
+      <c r="J74" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="K74" s="4">
+        <v/>
+      </c>
+      <c r="K74" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C75" s="8">
-        <v>100646</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F75" s="2">
-        <v>18</v>
-      </c>
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J75" s="3">
+      <c r="J75" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="K75" s="4">
+        <v/>
+      </c>
+      <c r="K75" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C76" s="8">
-        <v>100484</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F76" s="2">
-        <v>19</v>
-      </c>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I76" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>47.5</v>
-      </c>
-      <c r="K76" s="4">
+        <v/>
+      </c>
+      <c r="K76" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C77" s="9">
-        <v>100128</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F77" s="2">
-        <v>19</v>
-      </c>
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I77" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J77" s="3">
+      <c r="J77" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>47.5</v>
-      </c>
-      <c r="K77" s="4">
+        <v/>
+      </c>
+      <c r="K77" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C78" s="9">
-        <v>100224</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F78" s="2">
-        <v>20</v>
-      </c>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I78" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J78" s="3">
+      <c r="J78" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="K78" s="4">
+        <v/>
+      </c>
+      <c r="K78" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C79" s="9">
-        <v>100346</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F79" s="2">
-        <v>17</v>
-      </c>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="3">
         <f t="shared" si="5"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I79" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J79" s="3">
+      <c r="J79" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>42.5</v>
-      </c>
-      <c r="K79" s="4">
+        <v/>
+      </c>
+      <c r="K79" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>51</v>
+        <v/>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C80" s="9">
-        <v>100468</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F80" s="2">
-        <v>18</v>
-      </c>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I80" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J80" s="3">
+      <c r="J80" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="K80" s="4">
+        <v/>
+      </c>
+      <c r="K80" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C81" s="9">
-        <v>100474</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F81" s="2">
-        <v>17</v>
-      </c>
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="3">
         <f t="shared" si="5"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>42.5</v>
-      </c>
-      <c r="K81" s="4">
+        <v/>
+      </c>
+      <c r="K81" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>51</v>
+        <v/>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C82" s="9">
-        <v>100636</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F82" s="2">
-        <v>20</v>
-      </c>
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I82" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J82" s="3">
+      <c r="J82" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="K82" s="4">
+        <v/>
+      </c>
+      <c r="K82" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C83" s="9">
-        <v>100451</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F83" s="2">
-        <v>19</v>
-      </c>
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>47.5</v>
-      </c>
-      <c r="K83" s="4">
+        <v/>
+      </c>
+      <c r="K83" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C84" s="9">
-        <v>100605</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F84" s="2">
-        <v>16</v>
-      </c>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="3">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I84" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J84" s="3">
+      <c r="J84" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="K84" s="4">
+        <v/>
+      </c>
+      <c r="K84" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>57</v>
+        <v/>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C85" s="9">
-        <v>100429</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F85" s="2">
-        <v>18</v>
-      </c>
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I85" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J85" s="3">
+      <c r="J85" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="K85" s="4">
+        <v/>
+      </c>
+      <c r="K85" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C86" s="9">
-        <v>100637</v>
-      </c>
-      <c r="D86" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F86" s="2">
-        <v>20</v>
-      </c>
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I86" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J86" s="3">
+      <c r="J86" s="3" t="str">
         <f t="shared" ref="J86:J149" si="8">IF(AND(C86="",F86="",G86=""),"",ROUND(H86+I86,2))</f>
-        <v>50</v>
-      </c>
-      <c r="K86" s="4">
+        <v/>
+      </c>
+      <c r="K86" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C87" s="9">
-        <v>100411</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F87" s="2">
-        <v>18</v>
-      </c>
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I87" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J87" s="3">
+      <c r="J87" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="K87" s="4">
+        <v/>
+      </c>
+      <c r="K87" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C88" s="9">
-        <v>100268</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F88" s="2">
-        <v>19</v>
-      </c>
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I88" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J88" s="3">
+      <c r="J88" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>47.5</v>
-      </c>
-      <c r="K88" s="4">
+        <v/>
+      </c>
+      <c r="K88" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C89" s="9">
-        <v>100416</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F89" s="2">
-        <v>19</v>
-      </c>
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>47.5</v>
-      </c>
-      <c r="K89" s="4">
+        <v/>
+      </c>
+      <c r="K89" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C90" s="9">
-        <v>100329</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F90" s="2">
-        <v>18</v>
-      </c>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I90" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J90" s="3">
+      <c r="J90" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="K90" s="4">
+        <v/>
+      </c>
+      <c r="K90" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C91" s="9">
-        <v>100264</v>
-      </c>
-      <c r="D91" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F91" s="2">
-        <v>20</v>
-      </c>
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K91" s="4">
+        <v/>
+      </c>
+      <c r="K91" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C92" s="9">
-        <v>100617</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F92" s="2">
-        <v>19</v>
-      </c>
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I92" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J92" s="3">
+      <c r="J92" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>47.5</v>
-      </c>
-      <c r="K92" s="4">
+        <v/>
+      </c>
+      <c r="K92" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C93" s="9">
-        <v>100507</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="3">
@@ -4257,1104 +3841,746 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J93" s="3">
+      <c r="J93" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K93" s="4">
+        <v/>
+      </c>
+      <c r="K93" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>58</v>
+        <v/>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C94" s="9">
-        <v>100488</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F94" s="2">
-        <v>19</v>
-      </c>
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>47.5</v>
-      </c>
-      <c r="K94" s="4">
+        <v/>
+      </c>
+      <c r="K94" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C95" s="9">
-        <v>100436</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F95" s="2">
-        <v>17</v>
-      </c>
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="3">
         <f t="shared" si="5"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I95" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J95" s="3">
+      <c r="J95" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>42.5</v>
-      </c>
-      <c r="K95" s="4">
+        <v/>
+      </c>
+      <c r="K95" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>51</v>
+        <v/>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C96" s="9">
-        <v>800089</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F96" s="2">
-        <v>18</v>
-      </c>
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="K96" s="4">
+        <v/>
+      </c>
+      <c r="K96" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C97" s="9">
-        <v>100593</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F97" s="2">
-        <v>20</v>
-      </c>
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I97" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J97" s="3">
+      <c r="J97" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K97" s="4">
+        <v/>
+      </c>
+      <c r="K97" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C98" s="9">
-        <v>100585</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F98" s="2">
-        <v>20</v>
-      </c>
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I98" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J98" s="3">
+      <c r="J98" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K98" s="4">
+        <v/>
+      </c>
+      <c r="K98" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C99" s="9">
-        <v>100229</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F99" s="2">
-        <v>20</v>
-      </c>
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I99" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J99" s="3">
+      <c r="J99" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K99" s="4">
+        <v/>
+      </c>
+      <c r="K99" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C100" s="9">
-        <v>100227</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F100" s="2">
-        <v>20</v>
-      </c>
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K100" s="4">
+        <v/>
+      </c>
+      <c r="K100" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C101" s="9">
-        <v>100487</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F101" s="2">
-        <v>17</v>
-      </c>
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="3">
         <f t="shared" si="5"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>42.5</v>
-      </c>
-      <c r="K101" s="4">
+        <v/>
+      </c>
+      <c r="K101" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>51</v>
+        <v/>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C102" s="9">
-        <v>100460</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F102" s="2">
-        <v>20</v>
-      </c>
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K102" s="4">
+        <v/>
+      </c>
+      <c r="K102" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C103" s="9">
-        <v>100427</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F103" s="2">
-        <v>18</v>
-      </c>
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I103" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J103" s="3">
+      <c r="J103" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="K103" s="4">
+        <v/>
+      </c>
+      <c r="K103" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C104" s="9">
-        <v>100400</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F104" s="2">
-        <v>17</v>
-      </c>
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="3">
         <f t="shared" si="5"/>
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I104" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J104" s="3">
+      <c r="J104" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>42.5</v>
-      </c>
-      <c r="K104" s="4">
+        <v/>
+      </c>
+      <c r="K104" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>51</v>
+        <v/>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C105" s="9">
-        <v>100524</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F105" s="2">
-        <v>19</v>
-      </c>
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I105" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J105" s="3">
+      <c r="J105" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>47.5</v>
-      </c>
-      <c r="K105" s="4">
+        <v/>
+      </c>
+      <c r="K105" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C106" s="9">
-        <v>100277</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F106" s="2">
-        <v>20</v>
-      </c>
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I106" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J106" s="3">
+      <c r="J106" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K106" s="4">
+        <v/>
+      </c>
+      <c r="K106" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C107" s="9">
-        <v>100360</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F107" s="2">
-        <v>20</v>
-      </c>
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I107" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J107" s="3">
+      <c r="J107" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K107" s="4">
+        <v/>
+      </c>
+      <c r="K107" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C108" s="9">
-        <v>100522</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F108" s="2">
-        <v>20</v>
-      </c>
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I108" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J108" s="3">
+      <c r="J108" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K108" s="4">
+        <v/>
+      </c>
+      <c r="K108" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C109" s="9">
-        <v>100543</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F109" s="2">
-        <v>20</v>
-      </c>
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I109" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J109" s="3">
+      <c r="J109" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K109" s="4">
+        <v/>
+      </c>
+      <c r="K109" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C110" s="9">
-        <v>100359</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F110" s="2">
-        <v>20</v>
-      </c>
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I110" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J110" s="3">
+      <c r="J110" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K110" s="4">
+        <v/>
+      </c>
+      <c r="K110" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C111" s="9">
-        <v>100569</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F111" s="2">
-        <v>18</v>
-      </c>
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I111" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J111" s="3">
+      <c r="J111" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="K111" s="4">
+        <v/>
+      </c>
+      <c r="K111" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C112" s="9">
-        <v>800091</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F112" s="2">
-        <v>20</v>
-      </c>
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I112" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J112" s="3">
+      <c r="J112" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K112" s="4">
+        <v/>
+      </c>
+      <c r="K112" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C113" s="9">
-        <v>100229</v>
-      </c>
-      <c r="D113" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F113" s="2">
-        <v>20</v>
-      </c>
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I113" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J113" s="3">
+      <c r="J113" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K113" s="4">
+        <v/>
+      </c>
+      <c r="K113" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C114" s="9">
-        <v>800092</v>
-      </c>
-      <c r="D114" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F114" s="2">
-        <v>18</v>
-      </c>
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="3">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I114" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J114" s="3">
+      <c r="J114" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="K114" s="4">
+        <v/>
+      </c>
+      <c r="K114" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v/>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C115" s="9">
-        <v>100006</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F115" s="2">
-        <v>20</v>
-      </c>
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I115" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J115" s="3">
+      <c r="J115" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K115" s="4">
+        <v/>
+      </c>
+      <c r="K115" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C116" s="10">
-        <v>100042</v>
-      </c>
-      <c r="D116" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F116" s="2">
-        <v>20</v>
-      </c>
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I116" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J116" s="3">
+      <c r="J116" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K116" s="4">
+        <v/>
+      </c>
+      <c r="K116" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C117" s="9">
-        <v>100309</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F117" s="2">
-        <v>20</v>
-      </c>
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I117" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J117" s="3">
+      <c r="J117" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K117" s="4">
+        <v/>
+      </c>
+      <c r="K117" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C118" s="9">
-        <v>100601</v>
-      </c>
-      <c r="D118" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F118" s="2">
-        <v>20</v>
-      </c>
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I118" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J118" s="3">
+      <c r="J118" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K118" s="4">
+        <v/>
+      </c>
+      <c r="K118" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C119" s="10">
-        <v>100583</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F119" s="2">
-        <v>20</v>
-      </c>
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I119" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J119" s="3">
+      <c r="J119" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K119" s="4">
+        <v/>
+      </c>
+      <c r="K119" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C120" s="10">
-        <v>100073</v>
-      </c>
-      <c r="D120" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F120" s="2">
-        <v>19</v>
-      </c>
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="3">
         <f t="shared" si="5"/>
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="I120" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J120" s="3">
+      <c r="J120" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>47.5</v>
-      </c>
-      <c r="K120" s="4">
+        <v/>
+      </c>
+      <c r="K120" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v/>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C121" s="10">
-        <v>100545</v>
-      </c>
-      <c r="D121" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F121" s="2">
-        <v>20</v>
-      </c>
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I121" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J121" s="3">
+      <c r="J121" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K121" s="4">
+        <v/>
+      </c>
+      <c r="K121" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C122" s="10">
-        <v>100540</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F122" s="2">
-        <v>20</v>
-      </c>
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="3">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I122" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J122" s="3">
+      <c r="J122" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>50</v>
-      </c>
-      <c r="K122" s="4">
+        <v/>
+      </c>
+      <c r="K122" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C123" s="10">
-        <v>100574</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="3">
@@ -5365,31 +4591,21 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J123" s="3">
+      <c r="J123" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K123" s="4">
+        <v/>
+      </c>
+      <c r="K123" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>58</v>
+        <v/>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C124" s="10">
-        <v>100281</v>
-      </c>
-      <c r="D124" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="3">
@@ -5400,31 +4616,21 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J124" s="3">
+      <c r="J124" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K124" s="4">
+        <v/>
+      </c>
+      <c r="K124" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>58</v>
+        <v/>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C125" s="9">
-        <v>100532</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="3">
@@ -5435,31 +4641,21 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J125" s="3">
+      <c r="J125" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K125" s="4">
+        <v/>
+      </c>
+      <c r="K125" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>58</v>
+        <v/>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C126" s="9">
-        <v>100548</v>
-      </c>
-      <c r="D126" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="3">
@@ -5470,31 +4666,21 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J126" s="3">
+      <c r="J126" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K126" s="4">
+        <v/>
+      </c>
+      <c r="K126" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>58</v>
+        <v/>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C127" s="9">
-        <v>800090</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="3">
@@ -5505,31 +4691,21 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J127" s="3">
+      <c r="J127" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K127" s="4">
+        <v/>
+      </c>
+      <c r="K127" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>58</v>
+        <v/>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C128" s="8">
-        <v>100183</v>
-      </c>
-      <c r="D128" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="3">
@@ -5540,31 +4716,21 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J128" s="3">
+      <c r="J128" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K128" s="4">
+        <v/>
+      </c>
+      <c r="K128" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C129" s="8">
-        <v>100206</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="3">
@@ -5575,31 +4741,21 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J129" s="3">
+      <c r="J129" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K129" s="4">
+        <v/>
+      </c>
+      <c r="K129" s="4" t="str">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C130" s="8">
-        <v>100142</v>
-      </c>
-      <c r="D130" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="3">
@@ -5610,31 +4766,21 @@
         <f t="shared" ref="I130:I193" si="10">IF(OR(G130="",G130=0),0,ROUND(IF(G130&lt;=30,50,IF(G130&gt;=60,1,50-((G130-30)*(50/30)))),2))</f>
         <v>0</v>
       </c>
-      <c r="J130" s="3">
+      <c r="J130" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K130" s="4">
+        <v/>
+      </c>
+      <c r="K130" s="4" t="str">
         <f t="shared" ref="K130:K193" si="11">IF(J130="","",1+COUNTIFS($A$2:$A$501,A130,$B$2:$B$501,B130,$J$2:$J$501,"&gt;"&amp;J130))</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C131" s="8">
-        <v>100479</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="3">
@@ -5645,31 +4791,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J131" s="3">
+      <c r="J131" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K131" s="4">
+        <v/>
+      </c>
+      <c r="K131" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C132" s="8">
-        <v>100498</v>
-      </c>
-      <c r="D132" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="3">
@@ -5680,31 +4816,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J132" s="3">
+      <c r="J132" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K132" s="4">
+        <v/>
+      </c>
+      <c r="K132" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C133" s="8">
-        <v>100140</v>
-      </c>
-      <c r="D133" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="3">
@@ -5715,31 +4841,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J133" s="3">
+      <c r="J133" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K133" s="4">
+        <v/>
+      </c>
+      <c r="K133" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C134" s="8">
-        <v>100324</v>
-      </c>
-      <c r="D134" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="3">
@@ -5750,31 +4866,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J134" s="3">
+      <c r="J134" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K134" s="4">
+        <v/>
+      </c>
+      <c r="K134" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C135" s="8">
-        <v>100413</v>
-      </c>
-      <c r="D135" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="3">
@@ -5785,31 +4891,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J135" s="3">
+      <c r="J135" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K135" s="4">
+        <v/>
+      </c>
+      <c r="K135" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C136" s="8">
-        <v>100577</v>
-      </c>
-      <c r="D136" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="3">
@@ -5820,31 +4916,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J136" s="3">
+      <c r="J136" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K136" s="4">
+        <v/>
+      </c>
+      <c r="K136" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C137" s="8">
-        <v>100642</v>
-      </c>
-      <c r="D137" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
       <c r="H137" s="3">
@@ -5855,31 +4941,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J137" s="3">
+      <c r="J137" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K137" s="4">
+        <v/>
+      </c>
+      <c r="K137" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C138" s="8">
-        <v>100646</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="3">
@@ -5890,31 +4966,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J138" s="3">
+      <c r="J138" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K138" s="4">
+        <v/>
+      </c>
+      <c r="K138" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C139" s="8">
-        <v>100484</v>
-      </c>
-      <c r="D139" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
       <c r="H139" s="3">
@@ -5925,31 +4991,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J139" s="3">
+      <c r="J139" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K139" s="4">
+        <v/>
+      </c>
+      <c r="K139" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C140" s="9">
-        <v>100128</v>
-      </c>
-      <c r="D140" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
       <c r="H140" s="3">
@@ -5960,31 +5016,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J140" s="3">
+      <c r="J140" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K140" s="4">
+        <v/>
+      </c>
+      <c r="K140" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C141" s="9">
-        <v>100224</v>
-      </c>
-      <c r="D141" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="3">
@@ -5995,31 +5041,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J141" s="3">
+      <c r="J141" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K141" s="4">
+        <v/>
+      </c>
+      <c r="K141" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C142" s="9">
-        <v>100346</v>
-      </c>
-      <c r="D142" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="3">
@@ -6030,31 +5066,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J142" s="3">
+      <c r="J142" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K142" s="4">
+        <v/>
+      </c>
+      <c r="K142" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C143" s="9">
-        <v>100468</v>
-      </c>
-      <c r="D143" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A143" s="2"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="3">
@@ -6065,31 +5091,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J143" s="3">
+      <c r="J143" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K143" s="4">
+        <v/>
+      </c>
+      <c r="K143" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C144" s="9">
-        <v>100474</v>
-      </c>
-      <c r="D144" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A144" s="2"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="3">
@@ -6100,31 +5116,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J144" s="3">
+      <c r="J144" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K144" s="4">
+        <v/>
+      </c>
+      <c r="K144" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C145" s="9">
-        <v>100636</v>
-      </c>
-      <c r="D145" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A145" s="2"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="3">
@@ -6135,31 +5141,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J145" s="3">
+      <c r="J145" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K145" s="4">
+        <v/>
+      </c>
+      <c r="K145" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C146" s="9">
-        <v>100451</v>
-      </c>
-      <c r="D146" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="3">
@@ -6170,31 +5166,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J146" s="3">
+      <c r="J146" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K146" s="4">
+        <v/>
+      </c>
+      <c r="K146" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C147" s="9">
-        <v>100605</v>
-      </c>
-      <c r="D147" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A147" s="2"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="3">
@@ -6205,31 +5191,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J147" s="3">
+      <c r="J147" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K147" s="4">
+        <v/>
+      </c>
+      <c r="K147" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C148" s="9">
-        <v>100429</v>
-      </c>
-      <c r="D148" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A148" s="2"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
       <c r="H148" s="3">
@@ -6240,31 +5216,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J148" s="3">
+      <c r="J148" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K148" s="4">
+        <v/>
+      </c>
+      <c r="K148" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C149" s="9">
-        <v>100637</v>
-      </c>
-      <c r="D149" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A149" s="2"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="3">
@@ -6275,31 +5241,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J149" s="3">
+      <c r="J149" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K149" s="4">
+        <v/>
+      </c>
+      <c r="K149" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C150" s="9">
-        <v>100411</v>
-      </c>
-      <c r="D150" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
       <c r="H150" s="3">
@@ -6310,31 +5266,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J150" s="3">
+      <c r="J150" s="3" t="str">
         <f t="shared" ref="J150:J213" si="12">IF(AND(C150="",F150="",G150=""),"",ROUND(H150+I150,2))</f>
-        <v>0</v>
-      </c>
-      <c r="K150" s="4">
+        <v/>
+      </c>
+      <c r="K150" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C151" s="9">
-        <v>100268</v>
-      </c>
-      <c r="D151" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A151" s="2"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
       <c r="H151" s="3">
@@ -6345,31 +5291,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J151" s="3">
+      <c r="J151" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K151" s="4">
+        <v/>
+      </c>
+      <c r="K151" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C152" s="9">
-        <v>100416</v>
-      </c>
-      <c r="D152" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A152" s="2"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="3">
@@ -6380,31 +5316,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J152" s="3">
+      <c r="J152" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K152" s="4">
+        <v/>
+      </c>
+      <c r="K152" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C153" s="9">
-        <v>100329</v>
-      </c>
-      <c r="D153" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A153" s="2"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
       <c r="H153" s="3">
@@ -6415,31 +5341,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J153" s="3">
+      <c r="J153" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K153" s="4">
+        <v/>
+      </c>
+      <c r="K153" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C154" s="9">
-        <v>100264</v>
-      </c>
-      <c r="D154" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A154" s="2"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="3">
@@ -6450,31 +5366,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J154" s="3">
+      <c r="J154" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K154" s="4">
+        <v/>
+      </c>
+      <c r="K154" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C155" s="9">
-        <v>100617</v>
-      </c>
-      <c r="D155" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A155" s="2"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="3">
@@ -6485,31 +5391,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J155" s="3">
+      <c r="J155" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K155" s="4">
+        <v/>
+      </c>
+      <c r="K155" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C156" s="9">
-        <v>100507</v>
-      </c>
-      <c r="D156" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A156" s="2"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="3">
@@ -6520,31 +5416,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J156" s="3">
+      <c r="J156" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K156" s="4">
+        <v/>
+      </c>
+      <c r="K156" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C157" s="9">
-        <v>100488</v>
-      </c>
-      <c r="D157" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A157" s="2"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="3">
@@ -6555,31 +5441,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J157" s="3">
+      <c r="J157" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K157" s="4">
+        <v/>
+      </c>
+      <c r="K157" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C158" s="9">
-        <v>100436</v>
-      </c>
-      <c r="D158" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="3">
@@ -6590,31 +5466,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J158" s="3">
+      <c r="J158" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K158" s="4">
+        <v/>
+      </c>
+      <c r="K158" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C159" s="9">
-        <v>800089</v>
-      </c>
-      <c r="D159" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="3">
@@ -6625,31 +5491,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J159" s="3">
+      <c r="J159" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K159" s="4">
+        <v/>
+      </c>
+      <c r="K159" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C160" s="9">
-        <v>100593</v>
-      </c>
-      <c r="D160" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="3">
@@ -6660,31 +5516,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J160" s="3">
+      <c r="J160" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K160" s="4">
+        <v/>
+      </c>
+      <c r="K160" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C161" s="9">
-        <v>100585</v>
-      </c>
-      <c r="D161" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="3">
@@ -6695,31 +5541,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J161" s="3">
+      <c r="J161" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K161" s="4">
+        <v/>
+      </c>
+      <c r="K161" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C162" s="9">
-        <v>100229</v>
-      </c>
-      <c r="D162" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="3">
@@ -6730,31 +5566,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J162" s="3">
+      <c r="J162" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K162" s="4">
+        <v/>
+      </c>
+      <c r="K162" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C163" s="9">
-        <v>100227</v>
-      </c>
-      <c r="D163" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A163" s="2"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="3">
@@ -6765,31 +5591,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J163" s="3">
+      <c r="J163" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K163" s="4">
+        <v/>
+      </c>
+      <c r="K163" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C164" s="9">
-        <v>100487</v>
-      </c>
-      <c r="D164" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="3">
@@ -6800,31 +5616,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J164" s="3">
+      <c r="J164" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K164" s="4">
+        <v/>
+      </c>
+      <c r="K164" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C165" s="9">
-        <v>100460</v>
-      </c>
-      <c r="D165" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A165" s="2"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="3">
@@ -6835,31 +5641,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J165" s="3">
+      <c r="J165" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K165" s="4">
+        <v/>
+      </c>
+      <c r="K165" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C166" s="9">
-        <v>100427</v>
-      </c>
-      <c r="D166" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="3">
@@ -6870,31 +5666,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J166" s="3">
+      <c r="J166" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K166" s="4">
+        <v/>
+      </c>
+      <c r="K166" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C167" s="9">
-        <v>100400</v>
-      </c>
-      <c r="D167" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="3">
@@ -6905,31 +5691,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J167" s="3">
+      <c r="J167" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K167" s="4">
+        <v/>
+      </c>
+      <c r="K167" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C168" s="9">
-        <v>100524</v>
-      </c>
-      <c r="D168" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="3">
@@ -6940,31 +5716,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J168" s="3">
+      <c r="J168" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K168" s="4">
+        <v/>
+      </c>
+      <c r="K168" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C169" s="9">
-        <v>100277</v>
-      </c>
-      <c r="D169" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="3">
@@ -6975,31 +5741,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J169" s="3">
+      <c r="J169" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K169" s="4">
+        <v/>
+      </c>
+      <c r="K169" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C170" s="9">
-        <v>100360</v>
-      </c>
-      <c r="D170" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="3">
@@ -7010,31 +5766,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J170" s="3">
+      <c r="J170" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K170" s="4">
+        <v/>
+      </c>
+      <c r="K170" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C171" s="9">
-        <v>100522</v>
-      </c>
-      <c r="D171" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="3">
@@ -7045,31 +5791,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J171" s="3">
+      <c r="J171" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K171" s="4">
+        <v/>
+      </c>
+      <c r="K171" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C172" s="9">
-        <v>100543</v>
-      </c>
-      <c r="D172" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="3">
@@ -7080,31 +5816,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J172" s="3">
+      <c r="J172" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K172" s="4">
+        <v/>
+      </c>
+      <c r="K172" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C173" s="9">
-        <v>100359</v>
-      </c>
-      <c r="D173" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="3">
@@ -7115,31 +5841,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J173" s="3">
+      <c r="J173" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K173" s="4">
+        <v/>
+      </c>
+      <c r="K173" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C174" s="9">
-        <v>100569</v>
-      </c>
-      <c r="D174" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="3">
@@ -7150,31 +5866,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J174" s="3">
+      <c r="J174" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K174" s="4">
+        <v/>
+      </c>
+      <c r="K174" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C175" s="9">
-        <v>800091</v>
-      </c>
-      <c r="D175" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="3">
@@ -7185,31 +5891,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J175" s="3">
+      <c r="J175" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K175" s="4">
+        <v/>
+      </c>
+      <c r="K175" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C176" s="9">
-        <v>100229</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="3">
@@ -7220,31 +5916,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J176" s="3">
+      <c r="J176" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K176" s="4">
+        <v/>
+      </c>
+      <c r="K176" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C177" s="9">
-        <v>800092</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A177" s="2"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="3">
@@ -7255,31 +5941,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J177" s="3">
+      <c r="J177" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K177" s="4">
+        <v/>
+      </c>
+      <c r="K177" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C178" s="9">
-        <v>100006</v>
-      </c>
-      <c r="D178" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A178" s="2"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="3">
@@ -7290,31 +5966,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J178" s="3">
+      <c r="J178" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K178" s="4">
+        <v/>
+      </c>
+      <c r="K178" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C179" s="10">
-        <v>100042</v>
-      </c>
-      <c r="D179" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A179" s="2"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="3">
@@ -7325,31 +5991,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J179" s="3">
+      <c r="J179" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K179" s="4">
+        <v/>
+      </c>
+      <c r="K179" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C180" s="9">
-        <v>100309</v>
-      </c>
-      <c r="D180" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A180" s="2"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="3">
@@ -7360,31 +6016,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J180" s="3">
+      <c r="J180" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K180" s="4">
+        <v/>
+      </c>
+      <c r="K180" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C181" s="9">
-        <v>100601</v>
-      </c>
-      <c r="D181" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A181" s="2"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="3">
@@ -7395,31 +6041,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J181" s="3">
+      <c r="J181" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K181" s="4">
+        <v/>
+      </c>
+      <c r="K181" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C182" s="10">
-        <v>100583</v>
-      </c>
-      <c r="D182" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A182" s="2"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="3">
@@ -7430,31 +6066,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J182" s="3">
+      <c r="J182" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K182" s="4">
+        <v/>
+      </c>
+      <c r="K182" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C183" s="10">
-        <v>100073</v>
-      </c>
-      <c r="D183" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A183" s="2"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="3">
@@ -7465,31 +6091,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J183" s="3">
+      <c r="J183" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K183" s="4">
+        <v/>
+      </c>
+      <c r="K183" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C184" s="10">
-        <v>100545</v>
-      </c>
-      <c r="D184" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A184" s="2"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="3">
@@ -7500,31 +6116,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J184" s="3">
+      <c r="J184" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K184" s="4">
+        <v/>
+      </c>
+      <c r="K184" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C185" s="10">
-        <v>100540</v>
-      </c>
-      <c r="D185" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A185" s="2"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="3">
@@ -7535,31 +6141,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J185" s="3">
+      <c r="J185" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K185" s="4">
+        <v/>
+      </c>
+      <c r="K185" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C186" s="10">
-        <v>100574</v>
-      </c>
-      <c r="D186" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A186" s="2"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="3">
@@ -7570,31 +6166,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J186" s="3">
+      <c r="J186" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K186" s="4">
+        <v/>
+      </c>
+      <c r="K186" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C187" s="10">
-        <v>100281</v>
-      </c>
-      <c r="D187" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A187" s="2"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="3">
@@ -7605,31 +6191,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J187" s="3">
+      <c r="J187" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K187" s="4">
+        <v/>
+      </c>
+      <c r="K187" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C188" s="9">
-        <v>100532</v>
-      </c>
-      <c r="D188" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A188" s="2"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="3">
@@ -7640,31 +6216,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J188" s="3">
+      <c r="J188" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K188" s="4">
+        <v/>
+      </c>
+      <c r="K188" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C189" s="9">
-        <v>100548</v>
-      </c>
-      <c r="D189" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A189" s="2"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="3">
@@ -7675,31 +6241,21 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J189" s="3">
+      <c r="J189" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K189" s="4">
+        <v/>
+      </c>
+      <c r="K189" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C190" s="9">
-        <v>800090</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A190" s="2"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="3">
@@ -7710,13 +6266,13 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J190" s="3">
+      <c r="J190" s="3" t="str">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K190" s="4">
+        <v/>
+      </c>
+      <c r="K190" s="4" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">

--- a/FFT Scoring Log.xlsx
+++ b/FFT Scoring Log.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siripes\Desktop\FFT_Ranking_Dashboard_Full_V1_1_FIXED\FFT_Ranking_Full_V1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siripes\Desktop\FFT ranking\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="97">
   <si>
     <t>Year</t>
   </si>
@@ -371,6 +371,12 @@
   </si>
   <si>
     <t>Security</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>July</t>
   </si>
 </sst>
 </file>
@@ -848,10 +854,10 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="9" width="12" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -922,7 +928,7 @@
       </c>
       <c r="K2" s="4">
         <f>IF(J2="","",1+COUNTIFS($A$2:$A$501,A2,$B$2:$B$501,B2,$J$2:$J$501,"&gt;"&amp;J2))</f>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -961,7 +967,7 @@
       </c>
       <c r="K3" s="4">
         <f t="shared" ref="K3:K65" si="3">IF(J3="","",1+COUNTIFS($A$2:$A$501,A3,$B$2:$B$501,B3,$J$2:$J$501,"&gt;"&amp;J3))</f>
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -980,23 +986,27 @@
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="F4" s="2">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2">
+        <v>51</v>
+      </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1031,7 +1041,7 @@
       </c>
       <c r="K5" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1070,7 +1080,7 @@
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1105,7 +1115,7 @@
       </c>
       <c r="K7" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1163,23 +1173,27 @@
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="F9" s="2">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2">
+        <v>49</v>
+      </c>
       <c r="H9" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>58.33</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1214,7 +1228,7 @@
       </c>
       <c r="K10" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1253,7 +1267,7 @@
       </c>
       <c r="K11" s="4">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1288,7 +1302,7 @@
       </c>
       <c r="K12" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1327,7 +1341,7 @@
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1362,7 +1376,7 @@
       </c>
       <c r="K14" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1381,23 +1395,27 @@
       <c r="E15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="F15" s="2">
+        <v>17</v>
+      </c>
+      <c r="G15" s="2">
+        <v>60</v>
+      </c>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1432,7 +1450,7 @@
       </c>
       <c r="K16" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1471,7 +1489,7 @@
       </c>
       <c r="K17" s="4">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1506,7 +1524,7 @@
       </c>
       <c r="K18" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1525,19 +1543,23 @@
       <c r="E19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="F19" s="2">
+        <v>17</v>
+      </c>
+      <c r="G19" s="2">
+        <v>52</v>
+      </c>
       <c r="H19" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>55.83</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
@@ -1576,7 +1598,7 @@
       </c>
       <c r="K20" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1595,23 +1617,27 @@
       <c r="E21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="F21" s="2">
+        <v>14</v>
+      </c>
+      <c r="G21" s="2">
+        <v>59</v>
+      </c>
       <c r="H21" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>36.67</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1646,7 +1672,7 @@
       </c>
       <c r="K22" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1685,7 +1711,7 @@
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1704,23 +1730,27 @@
       <c r="E24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="F24" s="2">
+        <v>14</v>
+      </c>
+      <c r="G24" s="2">
+        <v>57</v>
+      </c>
       <c r="H24" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1739,23 +1769,27 @@
       <c r="E25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="F25" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" s="2">
+        <v>51</v>
+      </c>
       <c r="H25" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J25" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>52.5</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1790,7 +1824,7 @@
       </c>
       <c r="K26" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1809,23 +1843,27 @@
       <c r="E27" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="F27" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" s="2">
+        <v>59</v>
+      </c>
       <c r="H27" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="J27" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>39.17</v>
       </c>
       <c r="K27" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1844,23 +1882,27 @@
       <c r="E28" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
+      <c r="F28" s="2">
+        <v>18</v>
+      </c>
+      <c r="G28" s="2">
+        <v>55</v>
+      </c>
       <c r="H28" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="J28" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1879,23 +1921,27 @@
       <c r="E29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
+      <c r="F29" s="2">
+        <v>16</v>
+      </c>
+      <c r="G29" s="2">
+        <v>50</v>
+      </c>
       <c r="H29" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="J29" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>56.67</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1914,23 +1960,27 @@
       <c r="E30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
+      <c r="F30" s="2">
+        <v>17</v>
+      </c>
+      <c r="G30" s="2">
+        <v>50</v>
+      </c>
       <c r="H30" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>59.17</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1965,7 +2015,7 @@
       </c>
       <c r="K31" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2000,7 +2050,7 @@
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2035,7 +2085,7 @@
       </c>
       <c r="K33" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -2070,7 +2120,7 @@
       </c>
       <c r="K34" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2105,7 +2155,7 @@
       </c>
       <c r="K35" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -2140,7 +2190,7 @@
       </c>
       <c r="K36" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2175,7 +2225,7 @@
       </c>
       <c r="K37" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2194,23 +2244,27 @@
       <c r="E38" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
+      <c r="F38" s="2">
+        <v>12</v>
+      </c>
+      <c r="G38" s="2">
+        <v>50</v>
+      </c>
       <c r="H38" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I38" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="J38" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>46.67</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2229,23 +2283,27 @@
       <c r="E39" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
+      <c r="F39" s="2">
+        <v>16</v>
+      </c>
+      <c r="G39" s="2">
+        <v>47</v>
+      </c>
       <c r="H39" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I39" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21.67</v>
       </c>
       <c r="J39" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>61.67</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2264,23 +2322,27 @@
       <c r="E40" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
+      <c r="F40" s="2">
+        <v>16</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45</v>
+      </c>
       <c r="H40" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I40" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J40" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="K40" s="4">
         <f>IF(J40="","",1+COUNTIFS($A$2:$A$501,A40,$B$2:$B$501,B40,$J$2:$J$501,"&gt;"&amp;J40))</f>
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2299,23 +2361,27 @@
       <c r="E41" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
+      <c r="F41" s="2">
+        <v>17</v>
+      </c>
+      <c r="G41" s="2">
+        <v>48</v>
+      </c>
       <c r="H41" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I41" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J41" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="K41" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2350,7 +2416,7 @@
       </c>
       <c r="K42" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2369,23 +2435,27 @@
       <c r="E43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
+      <c r="F43" s="2">
+        <v>18</v>
+      </c>
+      <c r="G43" s="2">
+        <v>55</v>
+      </c>
       <c r="H43" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I43" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="J43" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="K43" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2420,7 +2490,7 @@
       </c>
       <c r="K44" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2455,7 +2525,7 @@
       </c>
       <c r="K45" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2490,7 +2560,7 @@
       </c>
       <c r="K46" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2525,7 +2595,7 @@
       </c>
       <c r="K47" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2560,7 +2630,7 @@
       </c>
       <c r="K48" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2595,7 +2665,7 @@
       </c>
       <c r="K49" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2630,7 +2700,7 @@
       </c>
       <c r="K50" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2665,7 +2735,7 @@
       </c>
       <c r="K51" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2700,7 +2770,7 @@
       </c>
       <c r="K52" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2735,7 +2805,7 @@
       </c>
       <c r="K53" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2770,7 +2840,7 @@
       </c>
       <c r="K54" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2805,7 +2875,7 @@
       </c>
       <c r="K55" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2840,7 +2910,7 @@
       </c>
       <c r="K56" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2875,7 +2945,7 @@
       </c>
       <c r="K57" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2910,7 +2980,7 @@
       </c>
       <c r="K58" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2945,7 +3015,7 @@
       </c>
       <c r="K59" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2982,7 +3052,7 @@
       </c>
       <c r="K60" s="4">
         <f>IF(J60="","",1+COUNTIFS($A$2:$A$501,A60,$B$2:$B$501,B60,$J$2:$J$501,"&gt;"&amp;J60))</f>
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -3017,7 +3087,7 @@
       </c>
       <c r="K61" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -3052,7 +3122,7 @@
       </c>
       <c r="K62" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -3087,7 +3157,7 @@
       </c>
       <c r="K63" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -3122,715 +3192,1061 @@
       </c>
       <c r="K64" s="4">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
+      <c r="A65" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C65" s="8">
+        <v>100183</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F65" s="2">
+        <v>18</v>
+      </c>
       <c r="G65" s="2"/>
       <c r="H65" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I65" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="str">
+      <c r="J65" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K65" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K65" s="4">
         <f t="shared" si="3"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
+      <c r="A66" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C66" s="8">
+        <v>100206</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" s="2">
+        <v>20</v>
+      </c>
       <c r="G66" s="2"/>
       <c r="H66" s="3">
         <f t="shared" ref="H66:H129" si="5">IF(OR(F66="",F66=0),0,ROUND((F66/20)*50,2))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I66" s="3">
         <f t="shared" ref="I66:I129" si="6">IF(OR(G66="",G66=0),0,ROUND(IF(G66&lt;=30,50,IF(G66&gt;=60,1,50-((G66-30)*(50/30)))),2))</f>
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="str">
+      <c r="J66" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K66" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K66" s="4">
         <f t="shared" ref="K66:K129" si="7">IF(J66="","",1+COUNTIFS($A$2:$A$501,A66,$B$2:$B$501,B66,$J$2:$J$501,"&gt;"&amp;J66))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
+      <c r="A67" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C67" s="8">
+        <v>100142</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" s="2">
+        <v>20</v>
+      </c>
       <c r="G67" s="2"/>
       <c r="H67" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I67" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="str">
+      <c r="J67" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K67" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K67" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
+      <c r="A68" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C68" s="8">
+        <v>100479</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" s="2">
+        <v>19</v>
+      </c>
       <c r="G68" s="2"/>
       <c r="H68" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I68" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="str">
+      <c r="J68" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K68" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K68" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
+      <c r="A69" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C69" s="8">
+        <v>100498</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" s="2">
+        <v>18</v>
+      </c>
       <c r="G69" s="2"/>
       <c r="H69" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I69" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="str">
+      <c r="J69" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K69" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K69" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
+      <c r="A70" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C70" s="8">
+        <v>100140</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="2">
+        <v>17</v>
+      </c>
       <c r="G70" s="2"/>
       <c r="H70" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I70" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="str">
+      <c r="J70" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K70" s="4" t="str">
+        <v>42.5</v>
+      </c>
+      <c r="K70" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
+      <c r="A71" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C71" s="8">
+        <v>100324</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" s="2">
+        <v>20</v>
+      </c>
       <c r="G71" s="2"/>
       <c r="H71" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I71" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="str">
+      <c r="J71" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K71" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K71" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
+      <c r="A72" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C72" s="8">
+        <v>100413</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="2">
+        <v>19</v>
+      </c>
       <c r="G72" s="2"/>
       <c r="H72" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I72" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="str">
+      <c r="J72" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K72" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K72" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
+      <c r="A73" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C73" s="8">
+        <v>100577</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="2">
+        <v>20</v>
+      </c>
       <c r="G73" s="2"/>
       <c r="H73" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I73" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="str">
+      <c r="J73" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K73" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K73" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
+      <c r="A74" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C74" s="8">
+        <v>100642</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" s="2">
+        <v>20</v>
+      </c>
       <c r="G74" s="2"/>
       <c r="H74" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I74" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="str">
+      <c r="J74" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K74" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K74" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
+      <c r="A75" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C75" s="8">
+        <v>100646</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" s="2">
+        <v>18</v>
+      </c>
       <c r="G75" s="2"/>
       <c r="H75" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I75" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J75" s="3" t="str">
+      <c r="J75" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K75" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K75" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
+      <c r="A76" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C76" s="8">
+        <v>100484</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F76" s="2">
+        <v>19</v>
+      </c>
       <c r="G76" s="2"/>
       <c r="H76" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I76" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="str">
+      <c r="J76" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K76" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K76" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
+      <c r="A77" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" s="9">
+        <v>100128</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F77" s="2">
+        <v>19</v>
+      </c>
       <c r="G77" s="2"/>
       <c r="H77" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I77" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J77" s="3" t="str">
+      <c r="J77" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K77" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K77" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
+      <c r="A78" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C78" s="9">
+        <v>100224</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F78" s="2">
+        <v>20</v>
+      </c>
       <c r="G78" s="2"/>
       <c r="H78" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I78" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J78" s="3" t="str">
+      <c r="J78" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K78" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K78" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
+      <c r="A79" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C79" s="9">
+        <v>100346</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F79" s="2">
+        <v>17</v>
+      </c>
       <c r="G79" s="2"/>
       <c r="H79" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I79" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="str">
+      <c r="J79" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K79" s="4" t="str">
+        <v>42.5</v>
+      </c>
+      <c r="K79" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
+      <c r="A80" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C80" s="9">
+        <v>100468</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F80" s="2">
+        <v>18</v>
+      </c>
       <c r="G80" s="2"/>
       <c r="H80" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I80" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J80" s="3" t="str">
+      <c r="J80" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K80" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K80" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
+      <c r="A81" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C81" s="9">
+        <v>100474</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F81" s="2">
+        <v>17</v>
+      </c>
       <c r="G81" s="2"/>
       <c r="H81" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I81" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J81" s="3" t="str">
+      <c r="J81" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K81" s="4" t="str">
+        <v>42.5</v>
+      </c>
+      <c r="K81" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
+      <c r="A82" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C82" s="9">
+        <v>100636</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F82" s="2">
+        <v>20</v>
+      </c>
       <c r="G82" s="2"/>
       <c r="H82" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I82" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J82" s="3" t="str">
+      <c r="J82" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K82" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K82" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
+      <c r="A83" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C83" s="9">
+        <v>100451</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F83" s="2">
+        <v>19</v>
+      </c>
       <c r="G83" s="2"/>
       <c r="H83" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I83" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="str">
+      <c r="J83" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K83" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K83" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
+      <c r="A84" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C84" s="9">
+        <v>100605</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F84" s="2">
+        <v>16</v>
+      </c>
       <c r="G84" s="2"/>
       <c r="H84" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I84" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J84" s="3" t="str">
+      <c r="J84" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K84" s="4" t="str">
+        <v>40</v>
+      </c>
+      <c r="K84" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
+      <c r="A85" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" s="9">
+        <v>100429</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F85" s="2">
+        <v>18</v>
+      </c>
       <c r="G85" s="2"/>
       <c r="H85" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I85" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="str">
+      <c r="J85" s="3">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K85" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K85" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
+      <c r="A86" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86" s="9">
+        <v>100637</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F86" s="2">
+        <v>20</v>
+      </c>
       <c r="G86" s="2"/>
       <c r="H86" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I86" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J86" s="3" t="str">
+      <c r="J86" s="3">
         <f t="shared" ref="J86:J149" si="8">IF(AND(C86="",F86="",G86=""),"",ROUND(H86+I86,2))</f>
-        <v/>
-      </c>
-      <c r="K86" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K86" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
+      <c r="A87" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C87" s="9">
+        <v>100411</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F87" s="2">
+        <v>18</v>
+      </c>
       <c r="G87" s="2"/>
       <c r="H87" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I87" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="str">
+      <c r="J87" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K87" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K87" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
+      <c r="A88" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C88" s="9">
+        <v>100268</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F88" s="2">
+        <v>19</v>
+      </c>
       <c r="G88" s="2"/>
       <c r="H88" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I88" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J88" s="3" t="str">
+      <c r="J88" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K88" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K88" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
+      <c r="A89" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" s="9">
+        <v>100416</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F89" s="2">
+        <v>19</v>
+      </c>
       <c r="G89" s="2"/>
       <c r="H89" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I89" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J89" s="3" t="str">
+      <c r="J89" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K89" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K89" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
+      <c r="A90" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C90" s="9">
+        <v>100329</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F90" s="2">
+        <v>18</v>
+      </c>
       <c r="G90" s="2"/>
       <c r="H90" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I90" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="str">
+      <c r="J90" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K90" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K90" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
+      <c r="A91" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C91" s="9">
+        <v>100264</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F91" s="2">
+        <v>20</v>
+      </c>
       <c r="G91" s="2"/>
       <c r="H91" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I91" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="str">
+      <c r="J91" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K91" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K91" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
+      <c r="A92" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C92" s="9">
+        <v>100617</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F92" s="2">
+        <v>19</v>
+      </c>
       <c r="G92" s="2"/>
       <c r="H92" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I92" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="str">
+      <c r="J92" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K92" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K92" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
+      <c r="A93" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C93" s="9">
+        <v>100507</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="3">
@@ -3841,746 +4257,1104 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J93" s="3" t="str">
+      <c r="J93" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K93" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K93" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>58</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
+      <c r="A94" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C94" s="9">
+        <v>100488</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F94" s="2">
+        <v>19</v>
+      </c>
       <c r="G94" s="2"/>
       <c r="H94" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I94" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="str">
+      <c r="J94" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K94" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K94" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
+      <c r="A95" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C95" s="9">
+        <v>100436</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F95" s="2">
+        <v>17</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I95" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="str">
+      <c r="J95" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K95" s="4" t="str">
+        <v>42.5</v>
+      </c>
+      <c r="K95" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>51</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
+      <c r="A96" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C96" s="9">
+        <v>800089</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F96" s="2">
+        <v>18</v>
+      </c>
       <c r="G96" s="2"/>
       <c r="H96" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I96" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="str">
+      <c r="J96" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K96" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K96" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
+      <c r="A97" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C97" s="9">
+        <v>100593</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F97" s="2">
+        <v>20</v>
+      </c>
       <c r="G97" s="2"/>
       <c r="H97" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I97" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J97" s="3" t="str">
+      <c r="J97" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K97" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K97" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
+      <c r="A98" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C98" s="9">
+        <v>100585</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F98" s="2">
+        <v>20</v>
+      </c>
       <c r="G98" s="2"/>
       <c r="H98" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I98" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J98" s="3" t="str">
+      <c r="J98" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K98" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K98" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
+      <c r="A99" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C99" s="9">
+        <v>100229</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F99" s="2">
+        <v>20</v>
+      </c>
       <c r="G99" s="2"/>
       <c r="H99" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I99" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J99" s="3" t="str">
+      <c r="J99" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K99" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K99" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
+      <c r="A100" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C100" s="9">
+        <v>100227</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F100" s="2">
+        <v>20</v>
+      </c>
       <c r="G100" s="2"/>
       <c r="H100" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I100" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J100" s="3" t="str">
+      <c r="J100" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K100" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K100" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
+      <c r="A101" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C101" s="9">
+        <v>100487</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F101" s="2">
+        <v>17</v>
+      </c>
       <c r="G101" s="2"/>
       <c r="H101" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I101" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="str">
+      <c r="J101" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K101" s="4" t="str">
+        <v>42.5</v>
+      </c>
+      <c r="K101" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>51</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
+      <c r="A102" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C102" s="9">
+        <v>100460</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F102" s="2">
+        <v>20</v>
+      </c>
       <c r="G102" s="2"/>
       <c r="H102" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I102" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J102" s="3" t="str">
+      <c r="J102" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K102" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K102" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
+      <c r="A103" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C103" s="9">
+        <v>100427</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F103" s="2">
+        <v>18</v>
+      </c>
       <c r="G103" s="2"/>
       <c r="H103" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I103" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J103" s="3" t="str">
+      <c r="J103" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K103" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K103" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
+      <c r="A104" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C104" s="9">
+        <v>100400</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F104" s="2">
+        <v>17</v>
+      </c>
       <c r="G104" s="2"/>
       <c r="H104" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="I104" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J104" s="3" t="str">
+      <c r="J104" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K104" s="4" t="str">
+        <v>42.5</v>
+      </c>
+      <c r="K104" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>51</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
+      <c r="A105" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C105" s="9">
+        <v>100524</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F105" s="2">
+        <v>19</v>
+      </c>
       <c r="G105" s="2"/>
       <c r="H105" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I105" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J105" s="3" t="str">
+      <c r="J105" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K105" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K105" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
+      <c r="A106" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C106" s="9">
+        <v>100277</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F106" s="2">
+        <v>20</v>
+      </c>
       <c r="G106" s="2"/>
       <c r="H106" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I106" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J106" s="3" t="str">
+      <c r="J106" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K106" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K106" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
+      <c r="A107" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C107" s="9">
+        <v>100360</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F107" s="2">
+        <v>20</v>
+      </c>
       <c r="G107" s="2"/>
       <c r="H107" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I107" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J107" s="3" t="str">
+      <c r="J107" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K107" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K107" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
+      <c r="A108" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C108" s="9">
+        <v>100522</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F108" s="2">
+        <v>20</v>
+      </c>
       <c r="G108" s="2"/>
       <c r="H108" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I108" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J108" s="3" t="str">
+      <c r="J108" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K108" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K108" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
+      <c r="A109" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C109" s="9">
+        <v>100543</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F109" s="2">
+        <v>20</v>
+      </c>
       <c r="G109" s="2"/>
       <c r="H109" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I109" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J109" s="3" t="str">
+      <c r="J109" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K109" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K109" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
+      <c r="A110" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C110" s="9">
+        <v>100359</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F110" s="2">
+        <v>20</v>
+      </c>
       <c r="G110" s="2"/>
       <c r="H110" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I110" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J110" s="3" t="str">
+      <c r="J110" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K110" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K110" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
+      <c r="A111" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C111" s="9">
+        <v>100569</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F111" s="2">
+        <v>18</v>
+      </c>
       <c r="G111" s="2"/>
       <c r="H111" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I111" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J111" s="3" t="str">
+      <c r="J111" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K111" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K111" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
+      <c r="A112" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C112" s="9">
+        <v>800091</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F112" s="2">
+        <v>20</v>
+      </c>
       <c r="G112" s="2"/>
       <c r="H112" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I112" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J112" s="3" t="str">
+      <c r="J112" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K112" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K112" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
+      <c r="A113" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C113" s="9">
+        <v>100229</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F113" s="2">
+        <v>20</v>
+      </c>
       <c r="G113" s="2"/>
       <c r="H113" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I113" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J113" s="3" t="str">
+      <c r="J113" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K113" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K113" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
+      <c r="A114" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C114" s="9">
+        <v>800092</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F114" s="2">
+        <v>18</v>
+      </c>
       <c r="G114" s="2"/>
       <c r="H114" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I114" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J114" s="3" t="str">
+      <c r="J114" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K114" s="4" t="str">
+        <v>45</v>
+      </c>
+      <c r="K114" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>40</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
+      <c r="A115" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C115" s="9">
+        <v>100006</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F115" s="2">
+        <v>20</v>
+      </c>
       <c r="G115" s="2"/>
       <c r="H115" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I115" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J115" s="3" t="str">
+      <c r="J115" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K115" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K115" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
+      <c r="A116" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C116" s="10">
+        <v>100042</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F116" s="2">
+        <v>20</v>
+      </c>
       <c r="G116" s="2"/>
       <c r="H116" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I116" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J116" s="3" t="str">
+      <c r="J116" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K116" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K116" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
+      <c r="A117" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C117" s="9">
+        <v>100309</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F117" s="2">
+        <v>20</v>
+      </c>
       <c r="G117" s="2"/>
       <c r="H117" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I117" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J117" s="3" t="str">
+      <c r="J117" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K117" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K117" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
+      <c r="A118" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C118" s="9">
+        <v>100601</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F118" s="2">
+        <v>20</v>
+      </c>
       <c r="G118" s="2"/>
       <c r="H118" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I118" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J118" s="3" t="str">
+      <c r="J118" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K118" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K118" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="2"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
+      <c r="A119" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C119" s="10">
+        <v>100583</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F119" s="2">
+        <v>20</v>
+      </c>
       <c r="G119" s="2"/>
       <c r="H119" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I119" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J119" s="3" t="str">
+      <c r="J119" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K119" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K119" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="2"/>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
+      <c r="A120" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C120" s="10">
+        <v>100073</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F120" s="2">
+        <v>19</v>
+      </c>
       <c r="G120" s="2"/>
       <c r="H120" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="I120" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J120" s="3" t="str">
+      <c r="J120" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K120" s="4" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="K120" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="2"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
+      <c r="A121" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C121" s="10">
+        <v>100545</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F121" s="2">
+        <v>20</v>
+      </c>
       <c r="G121" s="2"/>
       <c r="H121" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I121" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J121" s="3" t="str">
+      <c r="J121" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K121" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K121" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="2"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
+      <c r="A122" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C122" s="10">
+        <v>100540</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F122" s="2">
+        <v>20</v>
+      </c>
       <c r="G122" s="2"/>
       <c r="H122" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I122" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J122" s="3" t="str">
+      <c r="J122" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K122" s="4" t="str">
+        <v>50</v>
+      </c>
+      <c r="K122" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
+      <c r="A123" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C123" s="10">
+        <v>100574</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="3">
@@ -4591,21 +5365,31 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J123" s="3" t="str">
+      <c r="J123" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K123" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K123" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>58</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
+      <c r="A124" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C124" s="10">
+        <v>100281</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="3">
@@ -4616,21 +5400,31 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J124" s="3" t="str">
+      <c r="J124" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K124" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K124" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>58</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
+      <c r="A125" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C125" s="9">
+        <v>100532</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="3">
@@ -4641,21 +5435,31 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J125" s="3" t="str">
+      <c r="J125" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K125" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K125" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>58</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" s="2"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
+      <c r="A126" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C126" s="9">
+        <v>100548</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="3">
@@ -4666,21 +5470,31 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J126" s="3" t="str">
+      <c r="J126" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K126" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K126" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>58</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" s="2"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
+      <c r="A127" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C127" s="9">
+        <v>800090</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="3">
@@ -4691,21 +5505,31 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J127" s="3" t="str">
+      <c r="J127" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K127" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K127" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" s="2"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
+      <c r="A128" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C128" s="8">
+        <v>100183</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="3">
@@ -4716,21 +5540,31 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J128" s="3" t="str">
+      <c r="J128" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K128" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K128" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
+      <c r="A129" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C129" s="8">
+        <v>100206</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="3">
@@ -4741,21 +5575,31 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J129" s="3" t="str">
+      <c r="J129" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K129" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K129" s="4">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130" s="2"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
+      <c r="A130" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C130" s="8">
+        <v>100142</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="3">
@@ -4766,21 +5610,31 @@
         <f t="shared" ref="I130:I193" si="10">IF(OR(G130="",G130=0),0,ROUND(IF(G130&lt;=30,50,IF(G130&gt;=60,1,50-((G130-30)*(50/30)))),2))</f>
         <v>0</v>
       </c>
-      <c r="J130" s="3" t="str">
+      <c r="J130" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K130" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K130" s="4">
         <f t="shared" ref="K130:K193" si="11">IF(J130="","",1+COUNTIFS($A$2:$A$501,A130,$B$2:$B$501,B130,$J$2:$J$501,"&gt;"&amp;J130))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131" s="2"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
+      <c r="A131" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C131" s="8">
+        <v>100479</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="3">
@@ -4791,21 +5645,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J131" s="3" t="str">
+      <c r="J131" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K131" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K131" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A132" s="2"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
+      <c r="A132" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C132" s="8">
+        <v>100498</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="3">
@@ -4816,21 +5680,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J132" s="3" t="str">
+      <c r="J132" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K132" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K132" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
+      <c r="A133" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C133" s="8">
+        <v>100140</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="3">
@@ -4841,21 +5715,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J133" s="3" t="str">
+      <c r="J133" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K133" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K133" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A134" s="2"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
+      <c r="A134" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C134" s="8">
+        <v>100324</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="3">
@@ -4866,21 +5750,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J134" s="3" t="str">
+      <c r="J134" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K134" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K134" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" s="2"/>
-      <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
+      <c r="A135" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C135" s="8">
+        <v>100413</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="3">
@@ -4891,21 +5785,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J135" s="3" t="str">
+      <c r="J135" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K135" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K135" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" s="2"/>
-      <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
+      <c r="A136" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C136" s="8">
+        <v>100577</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="3">
@@ -4916,21 +5820,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="str">
+      <c r="J136" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K136" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K136" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" s="2"/>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
+      <c r="A137" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C137" s="8">
+        <v>100642</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
       <c r="H137" s="3">
@@ -4941,21 +5855,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J137" s="3" t="str">
+      <c r="J137" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K137" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K137" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" s="2"/>
-      <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
+      <c r="A138" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C138" s="8">
+        <v>100646</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="3">
@@ -4966,21 +5890,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="str">
+      <c r="J138" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K138" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K138" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" s="2"/>
-      <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
+      <c r="A139" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C139" s="8">
+        <v>100484</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
       <c r="H139" s="3">
@@ -4991,21 +5925,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J139" s="3" t="str">
+      <c r="J139" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K139" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K139" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140" s="2"/>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
+      <c r="A140" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C140" s="9">
+        <v>100128</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
       <c r="H140" s="3">
@@ -5016,21 +5960,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J140" s="3" t="str">
+      <c r="J140" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K140" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K140" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141" s="2"/>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
+      <c r="A141" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C141" s="9">
+        <v>100224</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="3">
@@ -5041,21 +5995,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J141" s="3" t="str">
+      <c r="J141" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K141" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K141" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142" s="2"/>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
+      <c r="A142" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C142" s="9">
+        <v>100346</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="3">
@@ -5066,21 +6030,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J142" s="3" t="str">
+      <c r="J142" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K142" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K142" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143" s="2"/>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
+      <c r="A143" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C143" s="9">
+        <v>100468</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="3">
@@ -5091,21 +6065,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J143" s="3" t="str">
+      <c r="J143" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K143" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K143" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" s="2"/>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
+      <c r="A144" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C144" s="9">
+        <v>100474</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="3">
@@ -5116,21 +6100,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J144" s="3" t="str">
+      <c r="J144" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K144" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K144" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" s="2"/>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="A145" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C145" s="9">
+        <v>100636</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="3">
@@ -5141,21 +6135,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J145" s="3" t="str">
+      <c r="J145" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K145" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K145" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" s="2"/>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
+      <c r="A146" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C146" s="9">
+        <v>100451</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="3">
@@ -5166,21 +6170,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J146" s="3" t="str">
+      <c r="J146" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K146" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K146" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="2"/>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="A147" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C147" s="9">
+        <v>100605</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="3">
@@ -5191,21 +6205,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J147" s="3" t="str">
+      <c r="J147" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K147" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K147" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" s="2"/>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
+      <c r="A148" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C148" s="9">
+        <v>100429</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
       <c r="H148" s="3">
@@ -5216,21 +6240,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J148" s="3" t="str">
+      <c r="J148" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K148" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K148" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" s="2"/>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
+      <c r="A149" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C149" s="9">
+        <v>100637</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="3">
@@ -5241,21 +6275,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J149" s="3" t="str">
+      <c r="J149" s="3">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K149" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K149" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" s="2"/>
-      <c r="B150" s="2"/>
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
+      <c r="A150" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C150" s="9">
+        <v>100411</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
       <c r="H150" s="3">
@@ -5266,21 +6310,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J150" s="3" t="str">
+      <c r="J150" s="3">
         <f t="shared" ref="J150:J213" si="12">IF(AND(C150="",F150="",G150=""),"",ROUND(H150+I150,2))</f>
-        <v/>
-      </c>
-      <c r="K150" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K150" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151" s="2"/>
-      <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
+      <c r="A151" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C151" s="9">
+        <v>100268</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
       <c r="H151" s="3">
@@ -5291,21 +6345,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="str">
+      <c r="J151" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K151" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K151" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152" s="2"/>
-      <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
-      <c r="E152" s="2"/>
+      <c r="A152" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C152" s="9">
+        <v>100416</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="3">
@@ -5316,21 +6380,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J152" s="3" t="str">
+      <c r="J152" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K152" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K152" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153" s="2"/>
-      <c r="B153" s="2"/>
-      <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
-      <c r="E153" s="2"/>
+      <c r="A153" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C153" s="9">
+        <v>100329</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
       <c r="H153" s="3">
@@ -5341,21 +6415,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J153" s="3" t="str">
+      <c r="J153" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K153" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K153" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154" s="2"/>
-      <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
-      <c r="E154" s="2"/>
+      <c r="A154" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C154" s="9">
+        <v>100264</v>
+      </c>
+      <c r="D154" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="3">
@@ -5366,21 +6450,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J154" s="3" t="str">
+      <c r="J154" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K154" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K154" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155" s="2"/>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
-      <c r="E155" s="2"/>
+      <c r="A155" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C155" s="9">
+        <v>100617</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="3">
@@ -5391,21 +6485,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J155" s="3" t="str">
+      <c r="J155" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K155" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K155" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A156" s="2"/>
-      <c r="B156" s="2"/>
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
-      <c r="E156" s="2"/>
+      <c r="A156" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C156" s="9">
+        <v>100507</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="3">
@@ -5416,21 +6520,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J156" s="3" t="str">
+      <c r="J156" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K156" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K156" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157" s="2"/>
-      <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
-      <c r="E157" s="2"/>
+      <c r="A157" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C157" s="9">
+        <v>100488</v>
+      </c>
+      <c r="D157" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="3">
@@ -5441,21 +6555,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J157" s="3" t="str">
+      <c r="J157" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K157" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K157" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" s="2"/>
-      <c r="B158" s="2"/>
-      <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
-      <c r="E158" s="2"/>
+      <c r="A158" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C158" s="9">
+        <v>100436</v>
+      </c>
+      <c r="D158" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="3">
@@ -5466,21 +6590,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J158" s="3" t="str">
+      <c r="J158" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K158" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K158" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159" s="2"/>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
-      <c r="E159" s="2"/>
+      <c r="A159" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C159" s="9">
+        <v>800089</v>
+      </c>
+      <c r="D159" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="3">
@@ -5491,21 +6625,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J159" s="3" t="str">
+      <c r="J159" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K159" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K159" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A160" s="2"/>
-      <c r="B160" s="2"/>
-      <c r="C160" s="2"/>
-      <c r="D160" s="2"/>
-      <c r="E160" s="2"/>
+      <c r="A160" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C160" s="9">
+        <v>100593</v>
+      </c>
+      <c r="D160" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="3">
@@ -5516,21 +6660,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J160" s="3" t="str">
+      <c r="J160" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K160" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K160" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A161" s="2"/>
-      <c r="B161" s="2"/>
-      <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
-      <c r="E161" s="2"/>
+      <c r="A161" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C161" s="9">
+        <v>100585</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="3">
@@ -5541,21 +6695,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J161" s="3" t="str">
+      <c r="J161" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K161" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K161" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162" s="2"/>
-      <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
+      <c r="A162" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C162" s="9">
+        <v>100229</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="3">
@@ -5566,21 +6730,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J162" s="3" t="str">
+      <c r="J162" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K162" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K162" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A163" s="2"/>
-      <c r="B163" s="2"/>
-      <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
-      <c r="E163" s="2"/>
+      <c r="A163" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C163" s="9">
+        <v>100227</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="3">
@@ -5591,21 +6765,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J163" s="3" t="str">
+      <c r="J163" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K163" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K163" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A164" s="2"/>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
+      <c r="A164" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C164" s="9">
+        <v>100487</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="3">
@@ -5616,21 +6800,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J164" s="3" t="str">
+      <c r="J164" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K164" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K164" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A165" s="2"/>
-      <c r="B165" s="2"/>
-      <c r="C165" s="2"/>
-      <c r="D165" s="2"/>
-      <c r="E165" s="2"/>
+      <c r="A165" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C165" s="9">
+        <v>100460</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="3">
@@ -5641,21 +6835,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J165" s="3" t="str">
+      <c r="J165" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K165" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K165" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A166" s="2"/>
-      <c r="B166" s="2"/>
-      <c r="C166" s="2"/>
-      <c r="D166" s="2"/>
-      <c r="E166" s="2"/>
+      <c r="A166" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C166" s="9">
+        <v>100427</v>
+      </c>
+      <c r="D166" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="3">
@@ -5666,21 +6870,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J166" s="3" t="str">
+      <c r="J166" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K166" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K166" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="2"/>
-      <c r="B167" s="2"/>
-      <c r="C167" s="2"/>
-      <c r="D167" s="2"/>
-      <c r="E167" s="2"/>
+      <c r="A167" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C167" s="9">
+        <v>100400</v>
+      </c>
+      <c r="D167" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="3">
@@ -5691,21 +6905,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J167" s="3" t="str">
+      <c r="J167" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K167" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K167" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A168" s="2"/>
-      <c r="B168" s="2"/>
-      <c r="C168" s="2"/>
-      <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
+      <c r="A168" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C168" s="9">
+        <v>100524</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="3">
@@ -5716,21 +6940,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J168" s="3" t="str">
+      <c r="J168" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K168" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K168" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A169" s="2"/>
-      <c r="B169" s="2"/>
-      <c r="C169" s="2"/>
-      <c r="D169" s="2"/>
-      <c r="E169" s="2"/>
+      <c r="A169" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C169" s="9">
+        <v>100277</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="3">
@@ -5741,21 +6975,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J169" s="3" t="str">
+      <c r="J169" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K169" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K169" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A170" s="2"/>
-      <c r="B170" s="2"/>
-      <c r="C170" s="2"/>
-      <c r="D170" s="2"/>
-      <c r="E170" s="2"/>
+      <c r="A170" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C170" s="9">
+        <v>100360</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="3">
@@ -5766,21 +7010,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J170" s="3" t="str">
+      <c r="J170" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K170" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K170" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A171" s="2"/>
-      <c r="B171" s="2"/>
-      <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
-      <c r="E171" s="2"/>
+      <c r="A171" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C171" s="9">
+        <v>100522</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="3">
@@ -5791,21 +7045,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J171" s="3" t="str">
+      <c r="J171" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K171" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K171" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A172" s="2"/>
-      <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
+      <c r="A172" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C172" s="9">
+        <v>100543</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="3">
@@ -5816,21 +7080,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J172" s="3" t="str">
+      <c r="J172" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K172" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K172" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A173" s="2"/>
-      <c r="B173" s="2"/>
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
+      <c r="A173" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C173" s="9">
+        <v>100359</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="3">
@@ -5841,21 +7115,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J173" s="3" t="str">
+      <c r="J173" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K173" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K173" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A174" s="2"/>
-      <c r="B174" s="2"/>
-      <c r="C174" s="2"/>
-      <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
+      <c r="A174" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C174" s="9">
+        <v>100569</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="3">
@@ -5866,21 +7150,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J174" s="3" t="str">
+      <c r="J174" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K174" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K174" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A175" s="2"/>
-      <c r="B175" s="2"/>
-      <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
-      <c r="E175" s="2"/>
+      <c r="A175" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C175" s="9">
+        <v>800091</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="3">
@@ -5891,21 +7185,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J175" s="3" t="str">
+      <c r="J175" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K175" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K175" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A176" s="2"/>
-      <c r="B176" s="2"/>
-      <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
+      <c r="A176" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C176" s="9">
+        <v>100229</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="3">
@@ -5916,21 +7220,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J176" s="3" t="str">
+      <c r="J176" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K176" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K176" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A177" s="2"/>
-      <c r="B177" s="2"/>
-      <c r="C177" s="2"/>
-      <c r="D177" s="2"/>
-      <c r="E177" s="2"/>
+      <c r="A177" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C177" s="9">
+        <v>800092</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="3">
@@ -5941,21 +7255,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J177" s="3" t="str">
+      <c r="J177" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K177" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K177" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A178" s="2"/>
-      <c r="B178" s="2"/>
-      <c r="C178" s="2"/>
-      <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
+      <c r="A178" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C178" s="9">
+        <v>100006</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="3">
@@ -5966,21 +7290,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J178" s="3" t="str">
+      <c r="J178" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K178" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K178" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" s="2"/>
-      <c r="B179" s="2"/>
-      <c r="C179" s="2"/>
-      <c r="D179" s="2"/>
-      <c r="E179" s="2"/>
+      <c r="A179" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C179" s="10">
+        <v>100042</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="3">
@@ -5991,21 +7325,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J179" s="3" t="str">
+      <c r="J179" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K179" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K179" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180" s="2"/>
-      <c r="B180" s="2"/>
-      <c r="C180" s="2"/>
-      <c r="D180" s="2"/>
-      <c r="E180" s="2"/>
+      <c r="A180" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C180" s="9">
+        <v>100309</v>
+      </c>
+      <c r="D180" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="3">
@@ -6016,21 +7360,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J180" s="3" t="str">
+      <c r="J180" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K180" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K180" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A181" s="2"/>
-      <c r="B181" s="2"/>
-      <c r="C181" s="2"/>
-      <c r="D181" s="2"/>
-      <c r="E181" s="2"/>
+      <c r="A181" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C181" s="9">
+        <v>100601</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="3">
@@ -6041,21 +7395,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J181" s="3" t="str">
+      <c r="J181" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K181" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K181" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A182" s="2"/>
-      <c r="B182" s="2"/>
-      <c r="C182" s="2"/>
-      <c r="D182" s="2"/>
-      <c r="E182" s="2"/>
+      <c r="A182" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C182" s="10">
+        <v>100583</v>
+      </c>
+      <c r="D182" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="3">
@@ -6066,21 +7430,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J182" s="3" t="str">
+      <c r="J182" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K182" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K182" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A183" s="2"/>
-      <c r="B183" s="2"/>
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
-      <c r="E183" s="2"/>
+      <c r="A183" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C183" s="10">
+        <v>100073</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="3">
@@ -6091,21 +7465,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J183" s="3" t="str">
+      <c r="J183" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K183" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K183" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" s="2"/>
-      <c r="B184" s="2"/>
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
-      <c r="E184" s="2"/>
+      <c r="A184" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C184" s="10">
+        <v>100545</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="3">
@@ -6116,21 +7500,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J184" s="3" t="str">
+      <c r="J184" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K184" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K184" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185" s="2"/>
-      <c r="B185" s="2"/>
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
+      <c r="A185" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C185" s="10">
+        <v>100540</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="3">
@@ -6141,21 +7535,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J185" s="3" t="str">
+      <c r="J185" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K185" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K185" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A186" s="2"/>
-      <c r="B186" s="2"/>
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
+      <c r="A186" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C186" s="10">
+        <v>100574</v>
+      </c>
+      <c r="D186" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="3">
@@ -6166,21 +7570,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J186" s="3" t="str">
+      <c r="J186" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K186" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K186" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" s="2"/>
-      <c r="B187" s="2"/>
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
-      <c r="E187" s="2"/>
+      <c r="A187" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C187" s="10">
+        <v>100281</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="3">
@@ -6191,21 +7605,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J187" s="3" t="str">
+      <c r="J187" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K187" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K187" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" s="2"/>
-      <c r="B188" s="2"/>
-      <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
+      <c r="A188" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C188" s="9">
+        <v>100532</v>
+      </c>
+      <c r="D188" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="3">
@@ -6216,21 +7640,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J188" s="3" t="str">
+      <c r="J188" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K188" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K188" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" s="2"/>
-      <c r="B189" s="2"/>
-      <c r="C189" s="2"/>
-      <c r="D189" s="2"/>
-      <c r="E189" s="2"/>
+      <c r="A189" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C189" s="9">
+        <v>100548</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="3">
@@ -6241,21 +7675,31 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J189" s="3" t="str">
+      <c r="J189" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K189" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K189" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" s="2"/>
-      <c r="B190" s="2"/>
-      <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
+      <c r="A190" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C190" s="9">
+        <v>800090</v>
+      </c>
+      <c r="D190" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="3">
@@ -6266,13 +7710,13 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J190" s="3" t="str">
+      <c r="J190" s="3">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K190" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="K190" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">

--- a/FFT Scoring Log.xlsx
+++ b/FFT Scoring Log.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siripes\Desktop\FFT ranking\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siripes\Desktop\FFT Ranking Final Version\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -553,7 +553,9 @@
     <tableColumn id="6" name="Correct Answers (0-20)"/>
     <tableColumn id="7" name="Wearing Time (sec)"/>
     <tableColumn id="8" name="Exam Score"/>
-    <tableColumn id="9" name="Time Score"/>
+    <tableColumn id="9" name="Time Score">
+      <calculatedColumnFormula>IF(OR(G2="",G2=0),0,IF(G2&lt;=40,50,IF(G2&gt;=61,0,ROUND(50-((G2-40)*(49/20)),2))))</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="10" name="Total Score"/>
     <tableColumn id="11" name="Rank"/>
   </tableColumns>
@@ -856,8 +858,9 @@
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="26.28515625" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="9" width="12" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="14" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -919,11 +922,11 @@
         <v>0</v>
       </c>
       <c r="I2" s="3">
-        <f t="shared" ref="I2:I65" si="1">IF(OR(G2="",G2=0),0,ROUND(IF(G2&lt;=30,50,IF(G2&gt;=60,1,50-((G2-30)*(50/30)))),2))</f>
+        <f>IF(OR(G2="",G2=0),0,IF(G2&lt;=40,50,IF(G2&gt;=61,0,ROUND(50-((G2-40)*(49/20)),2))))</f>
         <v>0</v>
       </c>
       <c r="J2" s="3">
-        <f t="shared" ref="J2:J21" si="2">ROUND(H2+I2,2)</f>
+        <f t="shared" ref="J2:J21" si="1">ROUND(H2+I2,2)</f>
         <v>0</v>
       </c>
       <c r="K2" s="4">
@@ -958,12 +961,12 @@
         <v>42.5</v>
       </c>
       <c r="I3" s="3">
+        <f t="shared" ref="I3:I66" si="2">IF(OR(G3="",G3=0),0,IF(G3&lt;=40,50,IF(G3&gt;=61,0,ROUND(50-((G3-40)*(49/20)),2))))</f>
+        <v>5.9</v>
+      </c>
+      <c r="J3" s="3">
         <f t="shared" si="1"/>
-        <v>3.33</v>
-      </c>
-      <c r="J3" s="3">
-        <f t="shared" si="2"/>
-        <v>45.83</v>
+        <v>48.4</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" ref="K3:K65" si="3">IF(J3="","",1+COUNTIFS($A$2:$A$501,A3,$B$2:$B$501,B3,$J$2:$J$501,"&gt;"&amp;J3))</f>
@@ -997,12 +1000,12 @@
         <v>40</v>
       </c>
       <c r="I4" s="3">
+        <f t="shared" si="2"/>
+        <v>23.05</v>
+      </c>
+      <c r="J4" s="3">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="J4" s="3">
-        <f t="shared" si="2"/>
-        <v>55</v>
+        <v>63.05</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="3"/>
@@ -1032,11 +1035,11 @@
         <v>0</v>
       </c>
       <c r="I5" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K5" s="4">
@@ -1071,16 +1074,16 @@
         <v>47.5</v>
       </c>
       <c r="I6" s="3">
+        <f t="shared" si="2"/>
+        <v>5.9</v>
+      </c>
+      <c r="J6" s="3">
         <f t="shared" si="1"/>
-        <v>3.33</v>
-      </c>
-      <c r="J6" s="3">
-        <f t="shared" si="2"/>
-        <v>50.83</v>
+        <v>53.4</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1106,11 +1109,11 @@
         <v>0</v>
       </c>
       <c r="I7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K7" s="4">
@@ -1145,12 +1148,12 @@
         <v>45</v>
       </c>
       <c r="I8" s="3">
+        <f t="shared" si="2"/>
+        <v>35.299999999999997</v>
+      </c>
+      <c r="J8" s="3">
         <f t="shared" si="1"/>
-        <v>23.33</v>
-      </c>
-      <c r="J8" s="3">
-        <f t="shared" si="2"/>
-        <v>68.33</v>
+        <v>80.3</v>
       </c>
       <c r="K8" s="4">
         <f>IF(J8="","",1+COUNTIFS($A$2:$A$501,A8,$B$2:$B$501,B8,$J$2:$J$501,"&gt;"&amp;J8))</f>
@@ -1184,12 +1187,12 @@
         <v>40</v>
       </c>
       <c r="I9" s="3">
+        <f t="shared" si="2"/>
+        <v>27.95</v>
+      </c>
+      <c r="J9" s="3">
         <f t="shared" si="1"/>
-        <v>18.329999999999998</v>
-      </c>
-      <c r="J9" s="3">
-        <f t="shared" si="2"/>
-        <v>58.33</v>
+        <v>67.95</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="3"/>
@@ -1219,11 +1222,11 @@
         <v>0</v>
       </c>
       <c r="I10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K10" s="4">
@@ -1258,16 +1261,16 @@
         <v>42.5</v>
       </c>
       <c r="I11" s="3">
+        <f t="shared" si="2"/>
+        <v>3.45</v>
+      </c>
+      <c r="J11" s="3">
         <f t="shared" si="1"/>
-        <v>1.67</v>
-      </c>
-      <c r="J11" s="3">
-        <f t="shared" si="2"/>
-        <v>44.17</v>
+        <v>45.95</v>
       </c>
       <c r="K11" s="4">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1293,11 +1296,11 @@
         <v>0</v>
       </c>
       <c r="I12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K12" s="4">
@@ -1332,16 +1335,16 @@
         <v>45</v>
       </c>
       <c r="I13" s="3">
+        <f t="shared" si="2"/>
+        <v>18.149999999999999</v>
+      </c>
+      <c r="J13" s="3">
         <f t="shared" si="1"/>
-        <v>11.67</v>
-      </c>
-      <c r="J13" s="3">
-        <f t="shared" si="2"/>
-        <v>56.67</v>
+        <v>63.15</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1367,11 +1370,11 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K14" s="4">
@@ -1406,16 +1409,16 @@
         <v>42.5</v>
       </c>
       <c r="I15" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J15" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J15" s="3">
-        <f t="shared" si="2"/>
         <v>43.5</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1441,11 +1444,11 @@
         <v>0</v>
       </c>
       <c r="I16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K16" s="4">
@@ -1480,16 +1483,16 @@
         <v>40</v>
       </c>
       <c r="I17" s="3">
+        <f t="shared" si="2"/>
+        <v>15.7</v>
+      </c>
+      <c r="J17" s="3">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="J17" s="3">
-        <f t="shared" si="2"/>
-        <v>50</v>
+        <v>55.7</v>
       </c>
       <c r="K17" s="4">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1515,11 +1518,11 @@
         <v>0</v>
       </c>
       <c r="I18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K18" s="4">
@@ -1554,12 +1557,12 @@
         <v>42.5</v>
       </c>
       <c r="I19" s="3">
+        <f t="shared" si="2"/>
+        <v>20.6</v>
+      </c>
+      <c r="J19" s="3">
         <f t="shared" si="1"/>
-        <v>13.33</v>
-      </c>
-      <c r="J19" s="3">
-        <f t="shared" si="2"/>
-        <v>55.83</v>
+        <v>63.1</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="3"/>
@@ -1589,11 +1592,11 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K20" s="4">
@@ -1628,16 +1631,16 @@
         <v>35</v>
       </c>
       <c r="I21" s="3">
+        <f t="shared" si="2"/>
+        <v>3.45</v>
+      </c>
+      <c r="J21" s="3">
         <f t="shared" si="1"/>
-        <v>1.67</v>
-      </c>
-      <c r="J21" s="3">
-        <f t="shared" si="2"/>
-        <v>36.67</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1663,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J22" s="3">
@@ -1702,16 +1705,16 @@
         <v>37.5</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" si="1"/>
-        <v>11.67</v>
+        <f t="shared" si="2"/>
+        <v>18.149999999999999</v>
       </c>
       <c r="J23" s="3">
         <f t="shared" si="4"/>
-        <v>49.17</v>
+        <v>55.65</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1741,16 +1744,16 @@
         <v>35</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>8.35</v>
       </c>
       <c r="J24" s="3">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>43.35</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1780,16 +1783,16 @@
         <v>37.5</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f t="shared" si="2"/>
+        <v>23.05</v>
       </c>
       <c r="J25" s="3">
         <f t="shared" si="4"/>
-        <v>52.5</v>
+        <v>60.55</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1815,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J26" s="3">
@@ -1854,16 +1857,16 @@
         <v>37.5</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="1"/>
-        <v>1.67</v>
+        <f t="shared" si="2"/>
+        <v>3.45</v>
       </c>
       <c r="J27" s="3">
         <f t="shared" si="4"/>
-        <v>39.17</v>
+        <v>40.950000000000003</v>
       </c>
       <c r="K27" s="4">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1893,16 +1896,16 @@
         <v>45</v>
       </c>
       <c r="I28" s="3">
-        <f t="shared" si="1"/>
-        <v>8.33</v>
+        <f t="shared" si="2"/>
+        <v>13.25</v>
       </c>
       <c r="J28" s="3">
         <f t="shared" si="4"/>
-        <v>53.33</v>
+        <v>58.25</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1932,12 +1935,12 @@
         <v>40</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" si="1"/>
-        <v>16.670000000000002</v>
+        <f t="shared" si="2"/>
+        <v>25.5</v>
       </c>
       <c r="J29" s="3">
         <f t="shared" si="4"/>
-        <v>56.67</v>
+        <v>65.5</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="3"/>
@@ -1971,12 +1974,12 @@
         <v>42.5</v>
       </c>
       <c r="I30" s="3">
-        <f t="shared" si="1"/>
-        <v>16.670000000000002</v>
+        <f t="shared" si="2"/>
+        <v>25.5</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" si="4"/>
-        <v>59.17</v>
+        <v>68</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="3"/>
@@ -2006,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J31" s="3">
@@ -2041,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J32" s="3">
@@ -2076,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J33" s="3">
@@ -2111,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J34" s="3">
@@ -2146,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J35" s="3">
@@ -2181,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J36" s="3">
@@ -2216,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J37" s="3">
@@ -2255,16 +2258,16 @@
         <v>30</v>
       </c>
       <c r="I38" s="3">
-        <f t="shared" si="1"/>
-        <v>16.670000000000002</v>
+        <f t="shared" si="2"/>
+        <v>25.5</v>
       </c>
       <c r="J38" s="3">
         <f t="shared" si="4"/>
-        <v>46.67</v>
+        <v>55.5</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2294,12 +2297,12 @@
         <v>40</v>
       </c>
       <c r="I39" s="3">
-        <f t="shared" si="1"/>
-        <v>21.67</v>
+        <f t="shared" si="2"/>
+        <v>32.85</v>
       </c>
       <c r="J39" s="3">
         <f t="shared" si="4"/>
-        <v>61.67</v>
+        <v>72.849999999999994</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
@@ -2333,12 +2336,12 @@
         <v>40</v>
       </c>
       <c r="I40" s="3">
-        <f t="shared" si="1"/>
-        <v>25</v>
+        <f t="shared" si="2"/>
+        <v>37.75</v>
       </c>
       <c r="J40" s="3">
         <f t="shared" si="4"/>
-        <v>65</v>
+        <v>77.75</v>
       </c>
       <c r="K40" s="4">
         <f>IF(J40="","",1+COUNTIFS($A$2:$A$501,A40,$B$2:$B$501,B40,$J$2:$J$501,"&gt;"&amp;J40))</f>
@@ -2372,12 +2375,12 @@
         <v>42.5</v>
       </c>
       <c r="I41" s="3">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>30.4</v>
       </c>
       <c r="J41" s="3">
         <f t="shared" si="4"/>
-        <v>62.5</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="K41" s="4">
         <f t="shared" si="3"/>
@@ -2407,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J42" s="3">
@@ -2446,16 +2449,16 @@
         <v>45</v>
       </c>
       <c r="I43" s="3">
-        <f t="shared" si="1"/>
-        <v>8.33</v>
+        <f t="shared" si="2"/>
+        <v>13.25</v>
       </c>
       <c r="J43" s="3">
         <f t="shared" si="4"/>
-        <v>53.33</v>
+        <v>58.25</v>
       </c>
       <c r="K43" s="4">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2481,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J44" s="3">
@@ -2516,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J45" s="3">
@@ -2551,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J46" s="3">
@@ -2586,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J47" s="3">
@@ -2621,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J48" s="3">
@@ -2656,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J49" s="3">
@@ -2691,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J50" s="3">
@@ -2726,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J51" s="3">
@@ -2761,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J52" s="3">
@@ -2796,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J53" s="3">
@@ -2831,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J54" s="3">
@@ -2866,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J55" s="3">
@@ -2901,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J56" s="3">
@@ -2936,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J57" s="3">
@@ -2971,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J58" s="3">
@@ -3006,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J59" s="3">
@@ -3043,16 +3046,16 @@
         <v>0</v>
       </c>
       <c r="I60" s="3">
-        <f t="shared" si="1"/>
-        <v>31.67</v>
+        <f t="shared" si="2"/>
+        <v>47.55</v>
       </c>
       <c r="J60" s="3">
         <f t="shared" si="4"/>
-        <v>31.67</v>
+        <v>47.55</v>
       </c>
       <c r="K60" s="4">
         <f>IF(J60="","",1+COUNTIFS($A$2:$A$501,A60,$B$2:$B$501,B60,$J$2:$J$501,"&gt;"&amp;J60))</f>
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -3078,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J61" s="3">
@@ -3113,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J62" s="3">
@@ -3148,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J63" s="3">
@@ -3183,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J64" s="3">
@@ -3220,7 +3223,7 @@
         <v>45</v>
       </c>
       <c r="I65" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J65" s="3">
@@ -3257,7 +3260,7 @@
         <v>50</v>
       </c>
       <c r="I66" s="3">
-        <f t="shared" ref="I66:I129" si="6">IF(OR(G66="",G66=0),0,ROUND(IF(G66&lt;=30,50,IF(G66&gt;=60,1,50-((G66-30)*(50/30)))),2))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J66" s="3">
@@ -3265,7 +3268,7 @@
         <v>50</v>
       </c>
       <c r="K66" s="4">
-        <f t="shared" ref="K66:K129" si="7">IF(J66="","",1+COUNTIFS($A$2:$A$501,A66,$B$2:$B$501,B66,$J$2:$J$501,"&gt;"&amp;J66))</f>
+        <f t="shared" ref="K66:K129" si="6">IF(J66="","",1+COUNTIFS($A$2:$A$501,A66,$B$2:$B$501,B66,$J$2:$J$501,"&gt;"&amp;J66))</f>
         <v>1</v>
       </c>
     </row>
@@ -3294,7 +3297,7 @@
         <v>50</v>
       </c>
       <c r="I67" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I67:I130" si="7">IF(OR(G67="",G67=0),0,IF(G67&lt;=40,50,IF(G67&gt;=61,0,ROUND(50-((G67-40)*(49/20)),2))))</f>
         <v>0</v>
       </c>
       <c r="J67" s="3">
@@ -3302,7 +3305,7 @@
         <v>50</v>
       </c>
       <c r="K67" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -3331,7 +3334,7 @@
         <v>47.5</v>
       </c>
       <c r="I68" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J68" s="3">
@@ -3339,7 +3342,7 @@
         <v>47.5</v>
       </c>
       <c r="K68" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -3368,7 +3371,7 @@
         <v>45</v>
       </c>
       <c r="I69" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J69" s="3">
@@ -3376,7 +3379,7 @@
         <v>45</v>
       </c>
       <c r="K69" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -3405,7 +3408,7 @@
         <v>42.5</v>
       </c>
       <c r="I70" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J70" s="3">
@@ -3413,7 +3416,7 @@
         <v>42.5</v>
       </c>
       <c r="K70" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
     </row>
@@ -3442,7 +3445,7 @@
         <v>50</v>
       </c>
       <c r="I71" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J71" s="3">
@@ -3450,7 +3453,7 @@
         <v>50</v>
       </c>
       <c r="K71" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -3479,7 +3482,7 @@
         <v>47.5</v>
       </c>
       <c r="I72" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J72" s="3">
@@ -3487,7 +3490,7 @@
         <v>47.5</v>
       </c>
       <c r="K72" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -3516,7 +3519,7 @@
         <v>50</v>
       </c>
       <c r="I73" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J73" s="3">
@@ -3524,7 +3527,7 @@
         <v>50</v>
       </c>
       <c r="K73" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -3553,7 +3556,7 @@
         <v>50</v>
       </c>
       <c r="I74" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J74" s="3">
@@ -3561,7 +3564,7 @@
         <v>50</v>
       </c>
       <c r="K74" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -3590,7 +3593,7 @@
         <v>45</v>
       </c>
       <c r="I75" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J75" s="3">
@@ -3598,7 +3601,7 @@
         <v>45</v>
       </c>
       <c r="K75" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -3627,7 +3630,7 @@
         <v>47.5</v>
       </c>
       <c r="I76" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J76" s="3">
@@ -3635,7 +3638,7 @@
         <v>47.5</v>
       </c>
       <c r="K76" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -3664,7 +3667,7 @@
         <v>47.5</v>
       </c>
       <c r="I77" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J77" s="3">
@@ -3672,7 +3675,7 @@
         <v>47.5</v>
       </c>
       <c r="K77" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -3701,7 +3704,7 @@
         <v>50</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
@@ -3709,7 +3712,7 @@
         <v>50</v>
       </c>
       <c r="K78" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -3738,7 +3741,7 @@
         <v>42.5</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
@@ -3746,7 +3749,7 @@
         <v>42.5</v>
       </c>
       <c r="K79" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
     </row>
@@ -3775,7 +3778,7 @@
         <v>45</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
@@ -3783,7 +3786,7 @@
         <v>45</v>
       </c>
       <c r="K80" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -3812,7 +3815,7 @@
         <v>42.5</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
@@ -3820,7 +3823,7 @@
         <v>42.5</v>
       </c>
       <c r="K81" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
     </row>
@@ -3849,7 +3852,7 @@
         <v>50</v>
       </c>
       <c r="I82" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J82" s="3">
@@ -3857,7 +3860,7 @@
         <v>50</v>
       </c>
       <c r="K82" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -3886,7 +3889,7 @@
         <v>47.5</v>
       </c>
       <c r="I83" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J83" s="3">
@@ -3894,7 +3897,7 @@
         <v>47.5</v>
       </c>
       <c r="K83" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -3923,7 +3926,7 @@
         <v>40</v>
       </c>
       <c r="I84" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J84" s="3">
@@ -3931,7 +3934,7 @@
         <v>40</v>
       </c>
       <c r="K84" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>57</v>
       </c>
     </row>
@@ -3960,7 +3963,7 @@
         <v>45</v>
       </c>
       <c r="I85" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J85" s="3">
@@ -3968,7 +3971,7 @@
         <v>45</v>
       </c>
       <c r="K85" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -3997,7 +4000,7 @@
         <v>50</v>
       </c>
       <c r="I86" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J86" s="3">
@@ -4005,7 +4008,7 @@
         <v>50</v>
       </c>
       <c r="K86" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4034,7 +4037,7 @@
         <v>45</v>
       </c>
       <c r="I87" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J87" s="3">
@@ -4042,7 +4045,7 @@
         <v>45</v>
       </c>
       <c r="K87" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -4071,7 +4074,7 @@
         <v>47.5</v>
       </c>
       <c r="I88" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J88" s="3">
@@ -4079,7 +4082,7 @@
         <v>47.5</v>
       </c>
       <c r="K88" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -4108,7 +4111,7 @@
         <v>47.5</v>
       </c>
       <c r="I89" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J89" s="3">
@@ -4116,7 +4119,7 @@
         <v>47.5</v>
       </c>
       <c r="K89" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -4145,7 +4148,7 @@
         <v>45</v>
       </c>
       <c r="I90" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J90" s="3">
@@ -4153,7 +4156,7 @@
         <v>45</v>
       </c>
       <c r="K90" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -4182,7 +4185,7 @@
         <v>50</v>
       </c>
       <c r="I91" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J91" s="3">
@@ -4190,7 +4193,7 @@
         <v>50</v>
       </c>
       <c r="K91" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4219,7 +4222,7 @@
         <v>47.5</v>
       </c>
       <c r="I92" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J92" s="3">
@@ -4227,7 +4230,7 @@
         <v>47.5</v>
       </c>
       <c r="K92" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -4254,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J93" s="3">
@@ -4262,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>58</v>
       </c>
     </row>
@@ -4291,7 +4294,7 @@
         <v>47.5</v>
       </c>
       <c r="I94" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J94" s="3">
@@ -4299,7 +4302,7 @@
         <v>47.5</v>
       </c>
       <c r="K94" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -4328,7 +4331,7 @@
         <v>42.5</v>
       </c>
       <c r="I95" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J95" s="3">
@@ -4336,7 +4339,7 @@
         <v>42.5</v>
       </c>
       <c r="K95" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
     </row>
@@ -4365,7 +4368,7 @@
         <v>45</v>
       </c>
       <c r="I96" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J96" s="3">
@@ -4373,7 +4376,7 @@
         <v>45</v>
       </c>
       <c r="K96" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -4402,7 +4405,7 @@
         <v>50</v>
       </c>
       <c r="I97" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J97" s="3">
@@ -4410,7 +4413,7 @@
         <v>50</v>
       </c>
       <c r="K97" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4439,7 +4442,7 @@
         <v>50</v>
       </c>
       <c r="I98" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J98" s="3">
@@ -4447,7 +4450,7 @@
         <v>50</v>
       </c>
       <c r="K98" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4476,7 +4479,7 @@
         <v>50</v>
       </c>
       <c r="I99" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J99" s="3">
@@ -4484,7 +4487,7 @@
         <v>50</v>
       </c>
       <c r="K99" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4513,7 +4516,7 @@
         <v>50</v>
       </c>
       <c r="I100" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J100" s="3">
@@ -4521,7 +4524,7 @@
         <v>50</v>
       </c>
       <c r="K100" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4550,7 +4553,7 @@
         <v>42.5</v>
       </c>
       <c r="I101" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J101" s="3">
@@ -4558,7 +4561,7 @@
         <v>42.5</v>
       </c>
       <c r="K101" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
     </row>
@@ -4587,7 +4590,7 @@
         <v>50</v>
       </c>
       <c r="I102" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J102" s="3">
@@ -4595,7 +4598,7 @@
         <v>50</v>
       </c>
       <c r="K102" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4624,7 +4627,7 @@
         <v>45</v>
       </c>
       <c r="I103" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J103" s="3">
@@ -4632,7 +4635,7 @@
         <v>45</v>
       </c>
       <c r="K103" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -4661,7 +4664,7 @@
         <v>42.5</v>
       </c>
       <c r="I104" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J104" s="3">
@@ -4669,7 +4672,7 @@
         <v>42.5</v>
       </c>
       <c r="K104" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>51</v>
       </c>
     </row>
@@ -4698,7 +4701,7 @@
         <v>47.5</v>
       </c>
       <c r="I105" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J105" s="3">
@@ -4706,7 +4709,7 @@
         <v>47.5</v>
       </c>
       <c r="K105" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -4735,7 +4738,7 @@
         <v>50</v>
       </c>
       <c r="I106" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J106" s="3">
@@ -4743,7 +4746,7 @@
         <v>50</v>
       </c>
       <c r="K106" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4772,7 +4775,7 @@
         <v>50</v>
       </c>
       <c r="I107" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J107" s="3">
@@ -4780,7 +4783,7 @@
         <v>50</v>
       </c>
       <c r="K107" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4809,7 +4812,7 @@
         <v>50</v>
       </c>
       <c r="I108" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J108" s="3">
@@ -4817,7 +4820,7 @@
         <v>50</v>
       </c>
       <c r="K108" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4846,7 +4849,7 @@
         <v>50</v>
       </c>
       <c r="I109" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J109" s="3">
@@ -4854,7 +4857,7 @@
         <v>50</v>
       </c>
       <c r="K109" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4883,7 +4886,7 @@
         <v>50</v>
       </c>
       <c r="I110" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J110" s="3">
@@ -4891,7 +4894,7 @@
         <v>50</v>
       </c>
       <c r="K110" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4920,7 +4923,7 @@
         <v>45</v>
       </c>
       <c r="I111" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J111" s="3">
@@ -4928,7 +4931,7 @@
         <v>45</v>
       </c>
       <c r="K111" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -4957,7 +4960,7 @@
         <v>50</v>
       </c>
       <c r="I112" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J112" s="3">
@@ -4965,7 +4968,7 @@
         <v>50</v>
       </c>
       <c r="K112" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -4994,7 +4997,7 @@
         <v>50</v>
       </c>
       <c r="I113" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J113" s="3">
@@ -5002,7 +5005,7 @@
         <v>50</v>
       </c>
       <c r="K113" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5031,7 +5034,7 @@
         <v>45</v>
       </c>
       <c r="I114" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J114" s="3">
@@ -5039,7 +5042,7 @@
         <v>45</v>
       </c>
       <c r="K114" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
@@ -5068,7 +5071,7 @@
         <v>50</v>
       </c>
       <c r="I115" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J115" s="3">
@@ -5076,7 +5079,7 @@
         <v>50</v>
       </c>
       <c r="K115" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5105,7 +5108,7 @@
         <v>50</v>
       </c>
       <c r="I116" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J116" s="3">
@@ -5113,7 +5116,7 @@
         <v>50</v>
       </c>
       <c r="K116" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5142,7 +5145,7 @@
         <v>50</v>
       </c>
       <c r="I117" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J117" s="3">
@@ -5150,7 +5153,7 @@
         <v>50</v>
       </c>
       <c r="K117" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5179,7 +5182,7 @@
         <v>50</v>
       </c>
       <c r="I118" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J118" s="3">
@@ -5187,7 +5190,7 @@
         <v>50</v>
       </c>
       <c r="K118" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5216,7 +5219,7 @@
         <v>50</v>
       </c>
       <c r="I119" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J119" s="3">
@@ -5224,7 +5227,7 @@
         <v>50</v>
       </c>
       <c r="K119" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5253,7 +5256,7 @@
         <v>47.5</v>
       </c>
       <c r="I120" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J120" s="3">
@@ -5261,7 +5264,7 @@
         <v>47.5</v>
       </c>
       <c r="K120" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
@@ -5290,7 +5293,7 @@
         <v>50</v>
       </c>
       <c r="I121" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J121" s="3">
@@ -5298,7 +5301,7 @@
         <v>50</v>
       </c>
       <c r="K121" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5327,7 +5330,7 @@
         <v>50</v>
       </c>
       <c r="I122" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J122" s="3">
@@ -5335,7 +5338,7 @@
         <v>50</v>
       </c>
       <c r="K122" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5362,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="I123" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J123" s="3">
@@ -5370,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>58</v>
       </c>
     </row>
@@ -5397,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J124" s="3">
@@ -5405,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>58</v>
       </c>
     </row>
@@ -5432,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J125" s="3">
@@ -5440,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>58</v>
       </c>
     </row>
@@ -5467,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="I126" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J126" s="3">
@@ -5475,7 +5478,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>58</v>
       </c>
     </row>
@@ -5502,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J127" s="3">
@@ -5510,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>58</v>
       </c>
     </row>
@@ -5537,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="I128" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J128" s="3">
@@ -5545,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="K128" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5572,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="I129" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J129" s="3">
@@ -5580,7 +5583,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -5607,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="I130" s="3">
-        <f t="shared" ref="I130:I193" si="10">IF(OR(G130="",G130=0),0,ROUND(IF(G130&lt;=30,50,IF(G130&gt;=60,1,50-((G130-30)*(50/30)))),2))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J130" s="3">
@@ -5615,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="K130" s="4">
-        <f t="shared" ref="K130:K193" si="11">IF(J130="","",1+COUNTIFS($A$2:$A$501,A130,$B$2:$B$501,B130,$J$2:$J$501,"&gt;"&amp;J130))</f>
+        <f t="shared" ref="K130:K193" si="10">IF(J130="","",1+COUNTIFS($A$2:$A$501,A130,$B$2:$B$501,B130,$J$2:$J$501,"&gt;"&amp;J130))</f>
         <v>1</v>
       </c>
     </row>
@@ -5642,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I131:I194" si="11">IF(OR(G131="",G131=0),0,IF(G131&lt;=40,50,IF(G131&gt;=61,0,ROUND(50-((G131-40)*(49/20)),2))))</f>
         <v>0</v>
       </c>
       <c r="J131" s="3">
@@ -5650,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5677,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="I132" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J132" s="3">
@@ -5685,7 +5688,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5712,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="I133" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J133" s="3">
@@ -5720,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5747,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J134" s="3">
@@ -5755,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5782,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="I135" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J135" s="3">
@@ -5790,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5817,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="I136" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J136" s="3">
@@ -5825,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5852,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J137" s="3">
@@ -5860,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5887,7 +5890,7 @@
         <v>0</v>
       </c>
       <c r="I138" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J138" s="3">
@@ -5895,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5922,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="I139" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J139" s="3">
@@ -5930,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="K139" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5957,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J140" s="3">
@@ -5965,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -5992,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="I141" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J141" s="3">
@@ -6000,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6027,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="I142" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J142" s="3">
@@ -6035,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="K142" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6062,7 +6065,7 @@
         <v>0</v>
       </c>
       <c r="I143" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J143" s="3">
@@ -6070,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="K143" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6097,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="I144" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J144" s="3">
@@ -6105,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="K144" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6132,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="I145" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J145" s="3">
@@ -6140,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="K145" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6167,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="I146" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J146" s="3">
@@ -6175,7 +6178,7 @@
         <v>0</v>
       </c>
       <c r="K146" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6202,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J147" s="3">
@@ -6210,7 +6213,7 @@
         <v>0</v>
       </c>
       <c r="K147" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6237,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="I148" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J148" s="3">
@@ -6245,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="K148" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6272,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="I149" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J149" s="3">
@@ -6280,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="K149" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6307,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="I150" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J150" s="3">
@@ -6315,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6342,7 +6345,7 @@
         <v>0</v>
       </c>
       <c r="I151" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J151" s="3">
@@ -6350,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="K151" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6377,7 +6380,7 @@
         <v>0</v>
       </c>
       <c r="I152" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J152" s="3">
@@ -6385,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="K152" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6412,7 +6415,7 @@
         <v>0</v>
       </c>
       <c r="I153" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J153" s="3">
@@ -6420,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="K153" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6447,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="I154" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J154" s="3">
@@ -6455,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="K154" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6482,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="I155" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J155" s="3">
@@ -6490,7 +6493,7 @@
         <v>0</v>
       </c>
       <c r="K155" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6517,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="I156" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J156" s="3">
@@ -6525,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="K156" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6552,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="I157" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J157" s="3">
@@ -6560,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="K157" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6587,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="I158" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J158" s="3">
@@ -6595,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="K158" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6622,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="I159" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J159" s="3">
@@ -6630,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="K159" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6657,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="I160" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J160" s="3">
@@ -6665,7 +6668,7 @@
         <v>0</v>
       </c>
       <c r="K160" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6692,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="I161" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J161" s="3">
@@ -6700,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="K161" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6727,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="I162" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J162" s="3">
@@ -6735,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="K162" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6762,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="I163" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J163" s="3">
@@ -6770,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="K163" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6797,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="I164" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J164" s="3">
@@ -6805,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="K164" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6832,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="I165" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J165" s="3">
@@ -6840,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="K165" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6867,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="I166" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J166" s="3">
@@ -6875,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="K166" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6902,7 +6905,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J167" s="3">
@@ -6910,7 +6913,7 @@
         <v>0</v>
       </c>
       <c r="K167" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6937,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="I168" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J168" s="3">
@@ -6945,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="K168" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -6972,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="I169" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J169" s="3">
@@ -6980,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="K169" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7007,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="I170" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J170" s="3">
@@ -7015,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="K170" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7042,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="I171" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J171" s="3">
@@ -7050,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="K171" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7077,7 +7080,7 @@
         <v>0</v>
       </c>
       <c r="I172" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J172" s="3">
@@ -7085,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="K172" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7112,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="I173" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J173" s="3">
@@ -7120,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="K173" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7147,7 +7150,7 @@
         <v>0</v>
       </c>
       <c r="I174" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J174" s="3">
@@ -7155,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="K174" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7182,7 +7185,7 @@
         <v>0</v>
       </c>
       <c r="I175" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J175" s="3">
@@ -7190,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="K175" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7217,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="I176" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J176" s="3">
@@ -7225,7 +7228,7 @@
         <v>0</v>
       </c>
       <c r="K176" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7252,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="I177" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J177" s="3">
@@ -7260,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="K177" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7287,7 +7290,7 @@
         <v>0</v>
       </c>
       <c r="I178" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J178" s="3">
@@ -7295,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="K178" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7322,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="I179" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J179" s="3">
@@ -7330,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="K179" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7357,7 +7360,7 @@
         <v>0</v>
       </c>
       <c r="I180" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J180" s="3">
@@ -7365,7 +7368,7 @@
         <v>0</v>
       </c>
       <c r="K180" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7392,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="I181" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J181" s="3">
@@ -7400,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="K181" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7427,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="I182" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J182" s="3">
@@ -7435,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="K182" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7462,7 +7465,7 @@
         <v>0</v>
       </c>
       <c r="I183" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J183" s="3">
@@ -7470,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="K183" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7497,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="I184" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J184" s="3">
@@ -7505,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="K184" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7532,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="I185" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J185" s="3">
@@ -7540,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="K185" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7567,7 +7570,7 @@
         <v>0</v>
       </c>
       <c r="I186" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J186" s="3">
@@ -7575,7 +7578,7 @@
         <v>0</v>
       </c>
       <c r="K186" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7602,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="I187" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J187" s="3">
@@ -7610,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="K187" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7637,7 +7640,7 @@
         <v>0</v>
       </c>
       <c r="I188" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J188" s="3">
@@ -7645,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="K188" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7672,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="I189" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J189" s="3">
@@ -7680,7 +7683,7 @@
         <v>0</v>
       </c>
       <c r="K189" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7707,7 +7710,7 @@
         <v>0</v>
       </c>
       <c r="I190" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J190" s="3">
@@ -7715,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="K190" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7732,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="I191" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J191" s="3" t="str">
@@ -7740,7 +7743,7 @@
         <v/>
       </c>
       <c r="K191" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7757,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="I192" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J192" s="3" t="str">
@@ -7765,7 +7768,7 @@
         <v/>
       </c>
       <c r="K192" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7782,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="I193" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J193" s="3" t="str">
@@ -7790,7 +7793,7 @@
         <v/>
       </c>
       <c r="K193" s="4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7807,7 +7810,7 @@
         <v>0</v>
       </c>
       <c r="I194" s="3">
-        <f t="shared" ref="I194:I257" si="14">IF(OR(G194="",G194=0),0,ROUND(IF(G194&lt;=30,50,IF(G194&gt;=60,1,50-((G194-30)*(50/30)))),2))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J194" s="3" t="str">
@@ -7815,7 +7818,7 @@
         <v/>
       </c>
       <c r="K194" s="4" t="str">
-        <f t="shared" ref="K194:K257" si="15">IF(J194="","",1+COUNTIFS($A$2:$A$501,A194,$B$2:$B$501,B194,$J$2:$J$501,"&gt;"&amp;J194))</f>
+        <f t="shared" ref="K194:K257" si="14">IF(J194="","",1+COUNTIFS($A$2:$A$501,A194,$B$2:$B$501,B194,$J$2:$J$501,"&gt;"&amp;J194))</f>
         <v/>
       </c>
     </row>
@@ -7832,7 +7835,7 @@
         <v>0</v>
       </c>
       <c r="I195" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="I195:I258" si="15">IF(OR(G195="",G195=0),0,IF(G195&lt;=40,50,IF(G195&gt;=61,0,ROUND(50-((G195-40)*(49/20)),2))))</f>
         <v>0</v>
       </c>
       <c r="J195" s="3" t="str">
@@ -7840,7 +7843,7 @@
         <v/>
       </c>
       <c r="K195" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -7857,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="I196" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J196" s="3" t="str">
@@ -7865,7 +7868,7 @@
         <v/>
       </c>
       <c r="K196" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -7882,7 +7885,7 @@
         <v>0</v>
       </c>
       <c r="I197" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J197" s="3" t="str">
@@ -7890,7 +7893,7 @@
         <v/>
       </c>
       <c r="K197" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -7907,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="I198" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J198" s="3" t="str">
@@ -7915,7 +7918,7 @@
         <v/>
       </c>
       <c r="K198" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -7932,7 +7935,7 @@
         <v>0</v>
       </c>
       <c r="I199" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J199" s="3" t="str">
@@ -7940,7 +7943,7 @@
         <v/>
       </c>
       <c r="K199" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -7957,7 +7960,7 @@
         <v>0</v>
       </c>
       <c r="I200" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J200" s="3" t="str">
@@ -7965,7 +7968,7 @@
         <v/>
       </c>
       <c r="K200" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -7982,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="I201" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J201" s="3" t="str">
@@ -7990,7 +7993,7 @@
         <v/>
       </c>
       <c r="K201" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8007,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="I202" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J202" s="3" t="str">
@@ -8015,7 +8018,7 @@
         <v/>
       </c>
       <c r="K202" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8032,7 +8035,7 @@
         <v>0</v>
       </c>
       <c r="I203" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J203" s="3" t="str">
@@ -8040,7 +8043,7 @@
         <v/>
       </c>
       <c r="K203" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8057,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="I204" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J204" s="3" t="str">
@@ -8065,7 +8068,7 @@
         <v/>
       </c>
       <c r="K204" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8082,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="I205" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J205" s="3" t="str">
@@ -8090,7 +8093,7 @@
         <v/>
       </c>
       <c r="K205" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8107,7 +8110,7 @@
         <v>0</v>
       </c>
       <c r="I206" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J206" s="3" t="str">
@@ -8115,7 +8118,7 @@
         <v/>
       </c>
       <c r="K206" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8132,7 +8135,7 @@
         <v>0</v>
       </c>
       <c r="I207" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J207" s="3" t="str">
@@ -8140,7 +8143,7 @@
         <v/>
       </c>
       <c r="K207" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8157,7 +8160,7 @@
         <v>0</v>
       </c>
       <c r="I208" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J208" s="3" t="str">
@@ -8165,7 +8168,7 @@
         <v/>
       </c>
       <c r="K208" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8182,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="I209" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J209" s="3" t="str">
@@ -8190,7 +8193,7 @@
         <v/>
       </c>
       <c r="K209" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8207,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="I210" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J210" s="3" t="str">
@@ -8215,7 +8218,7 @@
         <v/>
       </c>
       <c r="K210" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8232,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="I211" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J211" s="3" t="str">
@@ -8240,7 +8243,7 @@
         <v/>
       </c>
       <c r="K211" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8257,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="I212" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J212" s="3" t="str">
@@ -8265,7 +8268,7 @@
         <v/>
       </c>
       <c r="K212" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8282,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="I213" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J213" s="3" t="str">
@@ -8290,7 +8293,7 @@
         <v/>
       </c>
       <c r="K213" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8307,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="I214" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J214" s="3" t="str">
@@ -8315,7 +8318,7 @@
         <v/>
       </c>
       <c r="K214" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8332,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="I215" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J215" s="3" t="str">
@@ -8340,7 +8343,7 @@
         <v/>
       </c>
       <c r="K215" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8357,7 +8360,7 @@
         <v>0</v>
       </c>
       <c r="I216" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J216" s="3" t="str">
@@ -8365,7 +8368,7 @@
         <v/>
       </c>
       <c r="K216" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8382,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="I217" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J217" s="3" t="str">
@@ -8390,7 +8393,7 @@
         <v/>
       </c>
       <c r="K217" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8407,7 +8410,7 @@
         <v>0</v>
       </c>
       <c r="I218" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J218" s="3" t="str">
@@ -8415,7 +8418,7 @@
         <v/>
       </c>
       <c r="K218" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8432,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="I219" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J219" s="3" t="str">
@@ -8440,7 +8443,7 @@
         <v/>
       </c>
       <c r="K219" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8457,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="I220" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J220" s="3" t="str">
@@ -8465,7 +8468,7 @@
         <v/>
       </c>
       <c r="K220" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8482,7 +8485,7 @@
         <v>0</v>
       </c>
       <c r="I221" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J221" s="3" t="str">
@@ -8490,7 +8493,7 @@
         <v/>
       </c>
       <c r="K221" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8507,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="I222" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J222" s="3" t="str">
@@ -8515,7 +8518,7 @@
         <v/>
       </c>
       <c r="K222" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8532,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="I223" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J223" s="3" t="str">
@@ -8540,7 +8543,7 @@
         <v/>
       </c>
       <c r="K223" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8557,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="I224" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J224" s="3" t="str">
@@ -8565,7 +8568,7 @@
         <v/>
       </c>
       <c r="K224" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8582,7 +8585,7 @@
         <v>0</v>
       </c>
       <c r="I225" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J225" s="3" t="str">
@@ -8590,7 +8593,7 @@
         <v/>
       </c>
       <c r="K225" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8607,7 +8610,7 @@
         <v>0</v>
       </c>
       <c r="I226" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J226" s="3" t="str">
@@ -8615,7 +8618,7 @@
         <v/>
       </c>
       <c r="K226" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8632,7 +8635,7 @@
         <v>0</v>
       </c>
       <c r="I227" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J227" s="3" t="str">
@@ -8640,7 +8643,7 @@
         <v/>
       </c>
       <c r="K227" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8657,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="I228" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J228" s="3" t="str">
@@ -8665,7 +8668,7 @@
         <v/>
       </c>
       <c r="K228" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8682,7 +8685,7 @@
         <v>0</v>
       </c>
       <c r="I229" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J229" s="3" t="str">
@@ -8690,7 +8693,7 @@
         <v/>
       </c>
       <c r="K229" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8707,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="I230" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J230" s="3" t="str">
@@ -8715,7 +8718,7 @@
         <v/>
       </c>
       <c r="K230" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8732,7 +8735,7 @@
         <v>0</v>
       </c>
       <c r="I231" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J231" s="3" t="str">
@@ -8740,7 +8743,7 @@
         <v/>
       </c>
       <c r="K231" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8757,7 +8760,7 @@
         <v>0</v>
       </c>
       <c r="I232" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J232" s="3" t="str">
@@ -8765,7 +8768,7 @@
         <v/>
       </c>
       <c r="K232" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8782,7 +8785,7 @@
         <v>0</v>
       </c>
       <c r="I233" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J233" s="3" t="str">
@@ -8790,7 +8793,7 @@
         <v/>
       </c>
       <c r="K233" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8807,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="I234" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J234" s="3" t="str">
@@ -8815,7 +8818,7 @@
         <v/>
       </c>
       <c r="K234" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8832,7 +8835,7 @@
         <v>0</v>
       </c>
       <c r="I235" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J235" s="3" t="str">
@@ -8840,7 +8843,7 @@
         <v/>
       </c>
       <c r="K235" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8857,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="I236" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J236" s="3" t="str">
@@ -8865,7 +8868,7 @@
         <v/>
       </c>
       <c r="K236" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8882,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="I237" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J237" s="3" t="str">
@@ -8890,7 +8893,7 @@
         <v/>
       </c>
       <c r="K237" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8907,7 +8910,7 @@
         <v>0</v>
       </c>
       <c r="I238" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J238" s="3" t="str">
@@ -8915,7 +8918,7 @@
         <v/>
       </c>
       <c r="K238" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8932,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="I239" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J239" s="3" t="str">
@@ -8940,7 +8943,7 @@
         <v/>
       </c>
       <c r="K239" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8957,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="I240" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J240" s="3" t="str">
@@ -8965,7 +8968,7 @@
         <v/>
       </c>
       <c r="K240" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -8982,7 +8985,7 @@
         <v>0</v>
       </c>
       <c r="I241" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J241" s="3" t="str">
@@ -8990,7 +8993,7 @@
         <v/>
       </c>
       <c r="K241" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9007,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="I242" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J242" s="3" t="str">
@@ -9015,7 +9018,7 @@
         <v/>
       </c>
       <c r="K242" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9032,7 +9035,7 @@
         <v>0</v>
       </c>
       <c r="I243" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J243" s="3" t="str">
@@ -9040,7 +9043,7 @@
         <v/>
       </c>
       <c r="K243" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9057,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="I244" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J244" s="3" t="str">
@@ -9065,7 +9068,7 @@
         <v/>
       </c>
       <c r="K244" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9082,7 +9085,7 @@
         <v>0</v>
       </c>
       <c r="I245" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J245" s="3" t="str">
@@ -9090,7 +9093,7 @@
         <v/>
       </c>
       <c r="K245" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9107,7 +9110,7 @@
         <v>0</v>
       </c>
       <c r="I246" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J246" s="3" t="str">
@@ -9115,7 +9118,7 @@
         <v/>
       </c>
       <c r="K246" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9132,7 +9135,7 @@
         <v>0</v>
       </c>
       <c r="I247" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J247" s="3" t="str">
@@ -9140,7 +9143,7 @@
         <v/>
       </c>
       <c r="K247" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9157,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="I248" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J248" s="3" t="str">
@@ -9165,7 +9168,7 @@
         <v/>
       </c>
       <c r="K248" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9182,7 +9185,7 @@
         <v>0</v>
       </c>
       <c r="I249" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J249" s="3" t="str">
@@ -9190,7 +9193,7 @@
         <v/>
       </c>
       <c r="K249" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9207,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="I250" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J250" s="3" t="str">
@@ -9215,7 +9218,7 @@
         <v/>
       </c>
       <c r="K250" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9232,7 +9235,7 @@
         <v>0</v>
       </c>
       <c r="I251" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J251" s="3" t="str">
@@ -9240,7 +9243,7 @@
         <v/>
       </c>
       <c r="K251" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9257,7 +9260,7 @@
         <v>0</v>
       </c>
       <c r="I252" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J252" s="3" t="str">
@@ -9265,7 +9268,7 @@
         <v/>
       </c>
       <c r="K252" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9282,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="I253" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J253" s="3" t="str">
@@ -9290,7 +9293,7 @@
         <v/>
       </c>
       <c r="K253" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9307,7 +9310,7 @@
         <v>0</v>
       </c>
       <c r="I254" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J254" s="3" t="str">
@@ -9315,7 +9318,7 @@
         <v/>
       </c>
       <c r="K254" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9332,7 +9335,7 @@
         <v>0</v>
       </c>
       <c r="I255" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J255" s="3" t="str">
@@ -9340,7 +9343,7 @@
         <v/>
       </c>
       <c r="K255" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9357,7 +9360,7 @@
         <v>0</v>
       </c>
       <c r="I256" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J256" s="3" t="str">
@@ -9365,7 +9368,7 @@
         <v/>
       </c>
       <c r="K256" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9382,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="I257" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J257" s="3" t="str">
@@ -9390,7 +9393,7 @@
         <v/>
       </c>
       <c r="K257" s="4" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -9407,7 +9410,7 @@
         <v>0</v>
       </c>
       <c r="I258" s="3">
-        <f t="shared" ref="I258:I321" si="18">IF(OR(G258="",G258=0),0,ROUND(IF(G258&lt;=30,50,IF(G258&gt;=60,1,50-((G258-30)*(50/30)))),2))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J258" s="3" t="str">
@@ -9415,7 +9418,7 @@
         <v/>
       </c>
       <c r="K258" s="4" t="str">
-        <f t="shared" ref="K258:K321" si="19">IF(J258="","",1+COUNTIFS($A$2:$A$501,A258,$B$2:$B$501,B258,$J$2:$J$501,"&gt;"&amp;J258))</f>
+        <f t="shared" ref="K258:K321" si="18">IF(J258="","",1+COUNTIFS($A$2:$A$501,A258,$B$2:$B$501,B258,$J$2:$J$501,"&gt;"&amp;J258))</f>
         <v/>
       </c>
     </row>
@@ -9432,7 +9435,7 @@
         <v>0</v>
       </c>
       <c r="I259" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="I259:I322" si="19">IF(OR(G259="",G259=0),0,IF(G259&lt;=40,50,IF(G259&gt;=61,0,ROUND(50-((G259-40)*(49/20)),2))))</f>
         <v>0</v>
       </c>
       <c r="J259" s="3" t="str">
@@ -9440,7 +9443,7 @@
         <v/>
       </c>
       <c r="K259" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9457,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="I260" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J260" s="3" t="str">
@@ -9465,7 +9468,7 @@
         <v/>
       </c>
       <c r="K260" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9482,7 +9485,7 @@
         <v>0</v>
       </c>
       <c r="I261" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J261" s="3" t="str">
@@ -9490,7 +9493,7 @@
         <v/>
       </c>
       <c r="K261" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9507,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="I262" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J262" s="3" t="str">
@@ -9515,7 +9518,7 @@
         <v/>
       </c>
       <c r="K262" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9532,7 +9535,7 @@
         <v>0</v>
       </c>
       <c r="I263" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J263" s="3" t="str">
@@ -9540,7 +9543,7 @@
         <v/>
       </c>
       <c r="K263" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9557,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="I264" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J264" s="3" t="str">
@@ -9565,7 +9568,7 @@
         <v/>
       </c>
       <c r="K264" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9582,7 +9585,7 @@
         <v>0</v>
       </c>
       <c r="I265" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J265" s="3" t="str">
@@ -9590,7 +9593,7 @@
         <v/>
       </c>
       <c r="K265" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9607,7 +9610,7 @@
         <v>0</v>
       </c>
       <c r="I266" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J266" s="3" t="str">
@@ -9615,7 +9618,7 @@
         <v/>
       </c>
       <c r="K266" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9632,7 +9635,7 @@
         <v>0</v>
       </c>
       <c r="I267" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J267" s="3" t="str">
@@ -9640,7 +9643,7 @@
         <v/>
       </c>
       <c r="K267" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9657,7 +9660,7 @@
         <v>0</v>
       </c>
       <c r="I268" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J268" s="3" t="str">
@@ -9665,7 +9668,7 @@
         <v/>
       </c>
       <c r="K268" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9682,7 +9685,7 @@
         <v>0</v>
       </c>
       <c r="I269" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J269" s="3" t="str">
@@ -9690,7 +9693,7 @@
         <v/>
       </c>
       <c r="K269" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9707,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="I270" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J270" s="3" t="str">
@@ -9715,7 +9718,7 @@
         <v/>
       </c>
       <c r="K270" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9732,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="I271" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J271" s="3" t="str">
@@ -9740,7 +9743,7 @@
         <v/>
       </c>
       <c r="K271" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9757,7 +9760,7 @@
         <v>0</v>
       </c>
       <c r="I272" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J272" s="3" t="str">
@@ -9765,7 +9768,7 @@
         <v/>
       </c>
       <c r="K272" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9782,7 +9785,7 @@
         <v>0</v>
       </c>
       <c r="I273" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J273" s="3" t="str">
@@ -9790,7 +9793,7 @@
         <v/>
       </c>
       <c r="K273" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9807,7 +9810,7 @@
         <v>0</v>
       </c>
       <c r="I274" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J274" s="3" t="str">
@@ -9815,7 +9818,7 @@
         <v/>
       </c>
       <c r="K274" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9832,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="I275" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J275" s="3" t="str">
@@ -9840,7 +9843,7 @@
         <v/>
       </c>
       <c r="K275" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9857,7 +9860,7 @@
         <v>0</v>
       </c>
       <c r="I276" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J276" s="3" t="str">
@@ -9865,7 +9868,7 @@
         <v/>
       </c>
       <c r="K276" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9882,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="I277" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J277" s="3" t="str">
@@ -9890,7 +9893,7 @@
         <v/>
       </c>
       <c r="K277" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9907,7 +9910,7 @@
         <v>0</v>
       </c>
       <c r="I278" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J278" s="3" t="str">
@@ -9915,7 +9918,7 @@
         <v/>
       </c>
       <c r="K278" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9932,7 +9935,7 @@
         <v>0</v>
       </c>
       <c r="I279" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J279" s="3" t="str">
@@ -9940,7 +9943,7 @@
         <v/>
       </c>
       <c r="K279" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9957,7 +9960,7 @@
         <v>0</v>
       </c>
       <c r="I280" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J280" s="3" t="str">
@@ -9965,7 +9968,7 @@
         <v/>
       </c>
       <c r="K280" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9982,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="I281" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J281" s="3" t="str">
@@ -9990,7 +9993,7 @@
         <v/>
       </c>
       <c r="K281" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10007,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="I282" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J282" s="3" t="str">
@@ -10015,7 +10018,7 @@
         <v/>
       </c>
       <c r="K282" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10032,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="I283" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J283" s="3" t="str">
@@ -10040,7 +10043,7 @@
         <v/>
       </c>
       <c r="K283" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10057,7 +10060,7 @@
         <v>0</v>
       </c>
       <c r="I284" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J284" s="3" t="str">
@@ -10065,7 +10068,7 @@
         <v/>
       </c>
       <c r="K284" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10082,7 +10085,7 @@
         <v>0</v>
       </c>
       <c r="I285" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J285" s="3" t="str">
@@ -10090,7 +10093,7 @@
         <v/>
       </c>
       <c r="K285" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10107,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="I286" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J286" s="3" t="str">
@@ -10115,7 +10118,7 @@
         <v/>
       </c>
       <c r="K286" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10132,7 +10135,7 @@
         <v>0</v>
       </c>
       <c r="I287" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J287" s="3" t="str">
@@ -10140,7 +10143,7 @@
         <v/>
       </c>
       <c r="K287" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10157,7 +10160,7 @@
         <v>0</v>
       </c>
       <c r="I288" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J288" s="3" t="str">
@@ -10165,7 +10168,7 @@
         <v/>
       </c>
       <c r="K288" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10182,7 +10185,7 @@
         <v>0</v>
       </c>
       <c r="I289" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J289" s="3" t="str">
@@ -10190,7 +10193,7 @@
         <v/>
       </c>
       <c r="K289" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10207,7 +10210,7 @@
         <v>0</v>
       </c>
       <c r="I290" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J290" s="3" t="str">
@@ -10215,7 +10218,7 @@
         <v/>
       </c>
       <c r="K290" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10232,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="I291" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J291" s="3" t="str">
@@ -10240,7 +10243,7 @@
         <v/>
       </c>
       <c r="K291" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10257,7 +10260,7 @@
         <v>0</v>
       </c>
       <c r="I292" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J292" s="3" t="str">
@@ -10265,7 +10268,7 @@
         <v/>
       </c>
       <c r="K292" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10282,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="I293" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J293" s="3" t="str">
@@ -10290,7 +10293,7 @@
         <v/>
       </c>
       <c r="K293" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10307,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="I294" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J294" s="3" t="str">
@@ -10315,7 +10318,7 @@
         <v/>
       </c>
       <c r="K294" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10332,7 +10335,7 @@
         <v>0</v>
       </c>
       <c r="I295" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J295" s="3" t="str">
@@ -10340,7 +10343,7 @@
         <v/>
       </c>
       <c r="K295" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10357,7 +10360,7 @@
         <v>0</v>
       </c>
       <c r="I296" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J296" s="3" t="str">
@@ -10365,7 +10368,7 @@
         <v/>
       </c>
       <c r="K296" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10382,7 +10385,7 @@
         <v>0</v>
       </c>
       <c r="I297" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J297" s="3" t="str">
@@ -10390,7 +10393,7 @@
         <v/>
       </c>
       <c r="K297" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10407,7 +10410,7 @@
         <v>0</v>
       </c>
       <c r="I298" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J298" s="3" t="str">
@@ -10415,7 +10418,7 @@
         <v/>
       </c>
       <c r="K298" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10432,7 +10435,7 @@
         <v>0</v>
       </c>
       <c r="I299" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J299" s="3" t="str">
@@ -10440,7 +10443,7 @@
         <v/>
       </c>
       <c r="K299" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10457,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="I300" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J300" s="3" t="str">
@@ -10465,7 +10468,7 @@
         <v/>
       </c>
       <c r="K300" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10482,7 +10485,7 @@
         <v>0</v>
       </c>
       <c r="I301" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J301" s="3" t="str">
@@ -10490,7 +10493,7 @@
         <v/>
       </c>
       <c r="K301" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10507,7 +10510,7 @@
         <v>0</v>
       </c>
       <c r="I302" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J302" s="3" t="str">
@@ -10515,7 +10518,7 @@
         <v/>
       </c>
       <c r="K302" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10532,7 +10535,7 @@
         <v>0</v>
       </c>
       <c r="I303" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J303" s="3" t="str">
@@ -10540,7 +10543,7 @@
         <v/>
       </c>
       <c r="K303" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10557,7 +10560,7 @@
         <v>0</v>
       </c>
       <c r="I304" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J304" s="3" t="str">
@@ -10565,7 +10568,7 @@
         <v/>
       </c>
       <c r="K304" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10582,7 +10585,7 @@
         <v>0</v>
       </c>
       <c r="I305" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J305" s="3" t="str">
@@ -10590,7 +10593,7 @@
         <v/>
       </c>
       <c r="K305" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10607,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="I306" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J306" s="3" t="str">
@@ -10615,7 +10618,7 @@
         <v/>
       </c>
       <c r="K306" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10632,7 +10635,7 @@
         <v>0</v>
       </c>
       <c r="I307" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J307" s="3" t="str">
@@ -10640,7 +10643,7 @@
         <v/>
       </c>
       <c r="K307" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10657,7 +10660,7 @@
         <v>0</v>
       </c>
       <c r="I308" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J308" s="3" t="str">
@@ -10665,7 +10668,7 @@
         <v/>
       </c>
       <c r="K308" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10682,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="I309" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J309" s="3" t="str">
@@ -10690,7 +10693,7 @@
         <v/>
       </c>
       <c r="K309" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10707,7 +10710,7 @@
         <v>0</v>
       </c>
       <c r="I310" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J310" s="3" t="str">
@@ -10715,7 +10718,7 @@
         <v/>
       </c>
       <c r="K310" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10732,7 +10735,7 @@
         <v>0</v>
       </c>
       <c r="I311" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J311" s="3" t="str">
@@ -10740,7 +10743,7 @@
         <v/>
       </c>
       <c r="K311" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10757,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="I312" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J312" s="3" t="str">
@@ -10765,7 +10768,7 @@
         <v/>
       </c>
       <c r="K312" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10782,7 +10785,7 @@
         <v>0</v>
       </c>
       <c r="I313" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J313" s="3" t="str">
@@ -10790,7 +10793,7 @@
         <v/>
       </c>
       <c r="K313" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10807,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="I314" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J314" s="3" t="str">
@@ -10815,7 +10818,7 @@
         <v/>
       </c>
       <c r="K314" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10832,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="I315" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J315" s="3" t="str">
@@ -10840,7 +10843,7 @@
         <v/>
       </c>
       <c r="K315" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10857,7 +10860,7 @@
         <v>0</v>
       </c>
       <c r="I316" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J316" s="3" t="str">
@@ -10865,7 +10868,7 @@
         <v/>
       </c>
       <c r="K316" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10882,7 +10885,7 @@
         <v>0</v>
       </c>
       <c r="I317" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J317" s="3" t="str">
@@ -10890,7 +10893,7 @@
         <v/>
       </c>
       <c r="K317" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10907,7 +10910,7 @@
         <v>0</v>
       </c>
       <c r="I318" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J318" s="3" t="str">
@@ -10915,7 +10918,7 @@
         <v/>
       </c>
       <c r="K318" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10932,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="I319" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J319" s="3" t="str">
@@ -10940,7 +10943,7 @@
         <v/>
       </c>
       <c r="K319" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10957,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="I320" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J320" s="3" t="str">
@@ -10965,7 +10968,7 @@
         <v/>
       </c>
       <c r="K320" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -10982,7 +10985,7 @@
         <v>0</v>
       </c>
       <c r="I321" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J321" s="3" t="str">
@@ -10990,7 +10993,7 @@
         <v/>
       </c>
       <c r="K321" s="4" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -11007,7 +11010,7 @@
         <v>0</v>
       </c>
       <c r="I322" s="3">
-        <f t="shared" ref="I322:I385" si="22">IF(OR(G322="",G322=0),0,ROUND(IF(G322&lt;=30,50,IF(G322&gt;=60,1,50-((G322-30)*(50/30)))),2))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="J322" s="3" t="str">
@@ -11015,7 +11018,7 @@
         <v/>
       </c>
       <c r="K322" s="4" t="str">
-        <f t="shared" ref="K322:K385" si="23">IF(J322="","",1+COUNTIFS($A$2:$A$501,A322,$B$2:$B$501,B322,$J$2:$J$501,"&gt;"&amp;J322))</f>
+        <f t="shared" ref="K322:K385" si="22">IF(J322="","",1+COUNTIFS($A$2:$A$501,A322,$B$2:$B$501,B322,$J$2:$J$501,"&gt;"&amp;J322))</f>
         <v/>
       </c>
     </row>
@@ -11032,7 +11035,7 @@
         <v>0</v>
       </c>
       <c r="I323" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="I323:I386" si="23">IF(OR(G323="",G323=0),0,IF(G323&lt;=40,50,IF(G323&gt;=61,0,ROUND(50-((G323-40)*(49/20)),2))))</f>
         <v>0</v>
       </c>
       <c r="J323" s="3" t="str">
@@ -11040,7 +11043,7 @@
         <v/>
       </c>
       <c r="K323" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11057,7 +11060,7 @@
         <v>0</v>
       </c>
       <c r="I324" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J324" s="3" t="str">
@@ -11065,7 +11068,7 @@
         <v/>
       </c>
       <c r="K324" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11082,7 +11085,7 @@
         <v>0</v>
       </c>
       <c r="I325" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J325" s="3" t="str">
@@ -11090,7 +11093,7 @@
         <v/>
       </c>
       <c r="K325" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11107,7 +11110,7 @@
         <v>0</v>
       </c>
       <c r="I326" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J326" s="3" t="str">
@@ -11115,7 +11118,7 @@
         <v/>
       </c>
       <c r="K326" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11132,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="I327" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J327" s="3" t="str">
@@ -11140,7 +11143,7 @@
         <v/>
       </c>
       <c r="K327" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11157,7 +11160,7 @@
         <v>0</v>
       </c>
       <c r="I328" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J328" s="3" t="str">
@@ -11165,7 +11168,7 @@
         <v/>
       </c>
       <c r="K328" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11182,7 +11185,7 @@
         <v>0</v>
       </c>
       <c r="I329" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J329" s="3" t="str">
@@ -11190,7 +11193,7 @@
         <v/>
       </c>
       <c r="K329" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11207,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="I330" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J330" s="3" t="str">
@@ -11215,7 +11218,7 @@
         <v/>
       </c>
       <c r="K330" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11232,7 +11235,7 @@
         <v>0</v>
       </c>
       <c r="I331" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J331" s="3" t="str">
@@ -11240,7 +11243,7 @@
         <v/>
       </c>
       <c r="K331" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11257,7 +11260,7 @@
         <v>0</v>
       </c>
       <c r="I332" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J332" s="3" t="str">
@@ -11265,7 +11268,7 @@
         <v/>
       </c>
       <c r="K332" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11282,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="I333" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J333" s="3" t="str">
@@ -11290,7 +11293,7 @@
         <v/>
       </c>
       <c r="K333" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11307,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="I334" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J334" s="3" t="str">
@@ -11315,7 +11318,7 @@
         <v/>
       </c>
       <c r="K334" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11332,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="I335" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J335" s="3" t="str">
@@ -11340,7 +11343,7 @@
         <v/>
       </c>
       <c r="K335" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11357,7 +11360,7 @@
         <v>0</v>
       </c>
       <c r="I336" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J336" s="3" t="str">
@@ -11365,7 +11368,7 @@
         <v/>
       </c>
       <c r="K336" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11382,7 +11385,7 @@
         <v>0</v>
       </c>
       <c r="I337" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J337" s="3" t="str">
@@ -11390,7 +11393,7 @@
         <v/>
       </c>
       <c r="K337" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11407,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="I338" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J338" s="3" t="str">
@@ -11415,7 +11418,7 @@
         <v/>
       </c>
       <c r="K338" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11432,7 +11435,7 @@
         <v>0</v>
       </c>
       <c r="I339" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J339" s="3" t="str">
@@ -11440,7 +11443,7 @@
         <v/>
       </c>
       <c r="K339" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11457,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="I340" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J340" s="3" t="str">
@@ -11465,7 +11468,7 @@
         <v/>
       </c>
       <c r="K340" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11482,7 +11485,7 @@
         <v>0</v>
       </c>
       <c r="I341" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J341" s="3" t="str">
@@ -11490,7 +11493,7 @@
         <v/>
       </c>
       <c r="K341" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11507,7 +11510,7 @@
         <v>0</v>
       </c>
       <c r="I342" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J342" s="3" t="str">
@@ -11515,7 +11518,7 @@
         <v/>
       </c>
       <c r="K342" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11532,7 +11535,7 @@
         <v>0</v>
       </c>
       <c r="I343" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J343" s="3" t="str">
@@ -11540,7 +11543,7 @@
         <v/>
       </c>
       <c r="K343" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11557,7 +11560,7 @@
         <v>0</v>
       </c>
       <c r="I344" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J344" s="3" t="str">
@@ -11565,7 +11568,7 @@
         <v/>
       </c>
       <c r="K344" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11582,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="I345" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J345" s="3" t="str">
@@ -11590,7 +11593,7 @@
         <v/>
       </c>
       <c r="K345" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11607,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="I346" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J346" s="3" t="str">
@@ -11615,7 +11618,7 @@
         <v/>
       </c>
       <c r="K346" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11632,7 +11635,7 @@
         <v>0</v>
       </c>
       <c r="I347" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J347" s="3" t="str">
@@ -11640,7 +11643,7 @@
         <v/>
       </c>
       <c r="K347" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11657,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="I348" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J348" s="3" t="str">
@@ -11665,7 +11668,7 @@
         <v/>
       </c>
       <c r="K348" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11682,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="I349" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J349" s="3" t="str">
@@ -11690,7 +11693,7 @@
         <v/>
       </c>
       <c r="K349" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11707,7 +11710,7 @@
         <v>0</v>
       </c>
       <c r="I350" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J350" s="3" t="str">
@@ -11715,7 +11718,7 @@
         <v/>
       </c>
       <c r="K350" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11732,7 +11735,7 @@
         <v>0</v>
       </c>
       <c r="I351" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J351" s="3" t="str">
@@ -11740,7 +11743,7 @@
         <v/>
       </c>
       <c r="K351" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11757,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="I352" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J352" s="3" t="str">
@@ -11765,7 +11768,7 @@
         <v/>
       </c>
       <c r="K352" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11782,7 +11785,7 @@
         <v>0</v>
       </c>
       <c r="I353" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J353" s="3" t="str">
@@ -11790,7 +11793,7 @@
         <v/>
       </c>
       <c r="K353" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11807,7 +11810,7 @@
         <v>0</v>
       </c>
       <c r="I354" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J354" s="3" t="str">
@@ -11815,7 +11818,7 @@
         <v/>
       </c>
       <c r="K354" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11832,7 +11835,7 @@
         <v>0</v>
       </c>
       <c r="I355" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J355" s="3" t="str">
@@ -11840,7 +11843,7 @@
         <v/>
       </c>
       <c r="K355" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11857,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="I356" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J356" s="3" t="str">
@@ -11865,7 +11868,7 @@
         <v/>
       </c>
       <c r="K356" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11882,7 +11885,7 @@
         <v>0</v>
       </c>
       <c r="I357" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J357" s="3" t="str">
@@ -11890,7 +11893,7 @@
         <v/>
       </c>
       <c r="K357" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11907,7 +11910,7 @@
         <v>0</v>
       </c>
       <c r="I358" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J358" s="3" t="str">
@@ -11915,7 +11918,7 @@
         <v/>
       </c>
       <c r="K358" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11932,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="I359" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J359" s="3" t="str">
@@ -11940,7 +11943,7 @@
         <v/>
       </c>
       <c r="K359" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11957,7 +11960,7 @@
         <v>0</v>
       </c>
       <c r="I360" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J360" s="3" t="str">
@@ -11965,7 +11968,7 @@
         <v/>
       </c>
       <c r="K360" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -11982,7 +11985,7 @@
         <v>0</v>
       </c>
       <c r="I361" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J361" s="3" t="str">
@@ -11990,7 +11993,7 @@
         <v/>
       </c>
       <c r="K361" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12007,7 +12010,7 @@
         <v>0</v>
       </c>
       <c r="I362" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J362" s="3" t="str">
@@ -12015,7 +12018,7 @@
         <v/>
       </c>
       <c r="K362" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12032,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="I363" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J363" s="3" t="str">
@@ -12040,7 +12043,7 @@
         <v/>
       </c>
       <c r="K363" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12057,7 +12060,7 @@
         <v>0</v>
       </c>
       <c r="I364" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J364" s="3" t="str">
@@ -12065,7 +12068,7 @@
         <v/>
       </c>
       <c r="K364" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12082,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="I365" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J365" s="3" t="str">
@@ -12090,7 +12093,7 @@
         <v/>
       </c>
       <c r="K365" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12107,7 +12110,7 @@
         <v>0</v>
       </c>
       <c r="I366" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J366" s="3" t="str">
@@ -12115,7 +12118,7 @@
         <v/>
       </c>
       <c r="K366" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12132,7 +12135,7 @@
         <v>0</v>
       </c>
       <c r="I367" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J367" s="3" t="str">
@@ -12140,7 +12143,7 @@
         <v/>
       </c>
       <c r="K367" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12157,7 +12160,7 @@
         <v>0</v>
       </c>
       <c r="I368" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J368" s="3" t="str">
@@ -12165,7 +12168,7 @@
         <v/>
       </c>
       <c r="K368" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12182,7 +12185,7 @@
         <v>0</v>
       </c>
       <c r="I369" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J369" s="3" t="str">
@@ -12190,7 +12193,7 @@
         <v/>
       </c>
       <c r="K369" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12207,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="I370" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J370" s="3" t="str">
@@ -12215,7 +12218,7 @@
         <v/>
       </c>
       <c r="K370" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12232,7 +12235,7 @@
         <v>0</v>
       </c>
       <c r="I371" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J371" s="3" t="str">
@@ -12240,7 +12243,7 @@
         <v/>
       </c>
       <c r="K371" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12257,7 +12260,7 @@
         <v>0</v>
       </c>
       <c r="I372" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J372" s="3" t="str">
@@ -12265,7 +12268,7 @@
         <v/>
       </c>
       <c r="K372" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12282,7 +12285,7 @@
         <v>0</v>
       </c>
       <c r="I373" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J373" s="3" t="str">
@@ -12290,7 +12293,7 @@
         <v/>
       </c>
       <c r="K373" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12307,7 +12310,7 @@
         <v>0</v>
       </c>
       <c r="I374" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J374" s="3" t="str">
@@ -12315,7 +12318,7 @@
         <v/>
       </c>
       <c r="K374" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12332,7 +12335,7 @@
         <v>0</v>
       </c>
       <c r="I375" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J375" s="3" t="str">
@@ -12340,7 +12343,7 @@
         <v/>
       </c>
       <c r="K375" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12357,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="I376" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J376" s="3" t="str">
@@ -12365,7 +12368,7 @@
         <v/>
       </c>
       <c r="K376" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12382,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="I377" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J377" s="3" t="str">
@@ -12390,7 +12393,7 @@
         <v/>
       </c>
       <c r="K377" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12407,7 +12410,7 @@
         <v>0</v>
       </c>
       <c r="I378" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J378" s="3" t="str">
@@ -12415,7 +12418,7 @@
         <v/>
       </c>
       <c r="K378" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12432,7 +12435,7 @@
         <v>0</v>
       </c>
       <c r="I379" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J379" s="3" t="str">
@@ -12440,7 +12443,7 @@
         <v/>
       </c>
       <c r="K379" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12457,7 +12460,7 @@
         <v>0</v>
       </c>
       <c r="I380" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J380" s="3" t="str">
@@ -12465,7 +12468,7 @@
         <v/>
       </c>
       <c r="K380" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12482,7 +12485,7 @@
         <v>0</v>
       </c>
       <c r="I381" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J381" s="3" t="str">
@@ -12490,7 +12493,7 @@
         <v/>
       </c>
       <c r="K381" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12507,7 +12510,7 @@
         <v>0</v>
       </c>
       <c r="I382" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J382" s="3" t="str">
@@ -12515,7 +12518,7 @@
         <v/>
       </c>
       <c r="K382" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12532,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="I383" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J383" s="3" t="str">
@@ -12540,7 +12543,7 @@
         <v/>
       </c>
       <c r="K383" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12557,7 +12560,7 @@
         <v>0</v>
       </c>
       <c r="I384" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J384" s="3" t="str">
@@ -12565,7 +12568,7 @@
         <v/>
       </c>
       <c r="K384" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12582,7 +12585,7 @@
         <v>0</v>
       </c>
       <c r="I385" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J385" s="3" t="str">
@@ -12590,7 +12593,7 @@
         <v/>
       </c>
       <c r="K385" s="4" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -12607,7 +12610,7 @@
         <v>0</v>
       </c>
       <c r="I386" s="3">
-        <f t="shared" ref="I386:I449" si="26">IF(OR(G386="",G386=0),0,ROUND(IF(G386&lt;=30,50,IF(G386&gt;=60,1,50-((G386-30)*(50/30)))),2))</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J386" s="3" t="str">
@@ -12615,7 +12618,7 @@
         <v/>
       </c>
       <c r="K386" s="4" t="str">
-        <f t="shared" ref="K386:K449" si="27">IF(J386="","",1+COUNTIFS($A$2:$A$501,A386,$B$2:$B$501,B386,$J$2:$J$501,"&gt;"&amp;J386))</f>
+        <f t="shared" ref="K386:K449" si="26">IF(J386="","",1+COUNTIFS($A$2:$A$501,A386,$B$2:$B$501,B386,$J$2:$J$501,"&gt;"&amp;J386))</f>
         <v/>
       </c>
     </row>
@@ -12632,7 +12635,7 @@
         <v>0</v>
       </c>
       <c r="I387" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="I387:I450" si="27">IF(OR(G387="",G387=0),0,IF(G387&lt;=40,50,IF(G387&gt;=61,0,ROUND(50-((G387-40)*(49/20)),2))))</f>
         <v>0</v>
       </c>
       <c r="J387" s="3" t="str">
@@ -12640,7 +12643,7 @@
         <v/>
       </c>
       <c r="K387" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12657,7 +12660,7 @@
         <v>0</v>
       </c>
       <c r="I388" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J388" s="3" t="str">
@@ -12665,7 +12668,7 @@
         <v/>
       </c>
       <c r="K388" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12682,7 +12685,7 @@
         <v>0</v>
       </c>
       <c r="I389" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J389" s="3" t="str">
@@ -12690,7 +12693,7 @@
         <v/>
       </c>
       <c r="K389" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12707,7 +12710,7 @@
         <v>0</v>
       </c>
       <c r="I390" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J390" s="3" t="str">
@@ -12715,7 +12718,7 @@
         <v/>
       </c>
       <c r="K390" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12732,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="I391" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J391" s="3" t="str">
@@ -12740,7 +12743,7 @@
         <v/>
       </c>
       <c r="K391" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12757,7 +12760,7 @@
         <v>0</v>
       </c>
       <c r="I392" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J392" s="3" t="str">
@@ -12765,7 +12768,7 @@
         <v/>
       </c>
       <c r="K392" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12782,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="I393" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J393" s="3" t="str">
@@ -12790,7 +12793,7 @@
         <v/>
       </c>
       <c r="K393" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12807,7 +12810,7 @@
         <v>0</v>
       </c>
       <c r="I394" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J394" s="3" t="str">
@@ -12815,7 +12818,7 @@
         <v/>
       </c>
       <c r="K394" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12832,7 +12835,7 @@
         <v>0</v>
       </c>
       <c r="I395" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J395" s="3" t="str">
@@ -12840,7 +12843,7 @@
         <v/>
       </c>
       <c r="K395" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12857,7 +12860,7 @@
         <v>0</v>
       </c>
       <c r="I396" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J396" s="3" t="str">
@@ -12865,7 +12868,7 @@
         <v/>
       </c>
       <c r="K396" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12882,7 +12885,7 @@
         <v>0</v>
       </c>
       <c r="I397" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J397" s="3" t="str">
@@ -12890,7 +12893,7 @@
         <v/>
       </c>
       <c r="K397" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12907,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="I398" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J398" s="3" t="str">
@@ -12915,7 +12918,7 @@
         <v/>
       </c>
       <c r="K398" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12932,7 +12935,7 @@
         <v>0</v>
       </c>
       <c r="I399" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J399" s="3" t="str">
@@ -12940,7 +12943,7 @@
         <v/>
       </c>
       <c r="K399" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12957,7 +12960,7 @@
         <v>0</v>
       </c>
       <c r="I400" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J400" s="3" t="str">
@@ -12965,7 +12968,7 @@
         <v/>
       </c>
       <c r="K400" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -12982,7 +12985,7 @@
         <v>0</v>
       </c>
       <c r="I401" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J401" s="3" t="str">
@@ -12990,7 +12993,7 @@
         <v/>
       </c>
       <c r="K401" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13007,7 +13010,7 @@
         <v>0</v>
       </c>
       <c r="I402" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J402" s="3" t="str">
@@ -13015,7 +13018,7 @@
         <v/>
       </c>
       <c r="K402" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13032,7 +13035,7 @@
         <v>0</v>
       </c>
       <c r="I403" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J403" s="3" t="str">
@@ -13040,7 +13043,7 @@
         <v/>
       </c>
       <c r="K403" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13057,7 +13060,7 @@
         <v>0</v>
       </c>
       <c r="I404" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J404" s="3" t="str">
@@ -13065,7 +13068,7 @@
         <v/>
       </c>
       <c r="K404" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13082,7 +13085,7 @@
         <v>0</v>
       </c>
       <c r="I405" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J405" s="3" t="str">
@@ -13090,7 +13093,7 @@
         <v/>
       </c>
       <c r="K405" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13107,7 +13110,7 @@
         <v>0</v>
       </c>
       <c r="I406" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J406" s="3" t="str">
@@ -13115,7 +13118,7 @@
         <v/>
       </c>
       <c r="K406" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13132,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="I407" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J407" s="3" t="str">
@@ -13140,7 +13143,7 @@
         <v/>
       </c>
       <c r="K407" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13157,7 +13160,7 @@
         <v>0</v>
       </c>
       <c r="I408" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J408" s="3" t="str">
@@ -13165,7 +13168,7 @@
         <v/>
       </c>
       <c r="K408" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13182,7 +13185,7 @@
         <v>0</v>
       </c>
       <c r="I409" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J409" s="3" t="str">
@@ -13190,7 +13193,7 @@
         <v/>
       </c>
       <c r="K409" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13207,7 +13210,7 @@
         <v>0</v>
       </c>
       <c r="I410" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J410" s="3" t="str">
@@ -13215,7 +13218,7 @@
         <v/>
       </c>
       <c r="K410" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13232,7 +13235,7 @@
         <v>0</v>
       </c>
       <c r="I411" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J411" s="3" t="str">
@@ -13240,7 +13243,7 @@
         <v/>
       </c>
       <c r="K411" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13257,7 +13260,7 @@
         <v>0</v>
       </c>
       <c r="I412" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J412" s="3" t="str">
@@ -13265,7 +13268,7 @@
         <v/>
       </c>
       <c r="K412" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13282,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="I413" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J413" s="3" t="str">
@@ -13290,7 +13293,7 @@
         <v/>
       </c>
       <c r="K413" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13307,7 +13310,7 @@
         <v>0</v>
       </c>
       <c r="I414" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J414" s="3" t="str">
@@ -13315,7 +13318,7 @@
         <v/>
       </c>
       <c r="K414" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13332,7 +13335,7 @@
         <v>0</v>
       </c>
       <c r="I415" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J415" s="3" t="str">
@@ -13340,7 +13343,7 @@
         <v/>
       </c>
       <c r="K415" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13357,7 +13360,7 @@
         <v>0</v>
       </c>
       <c r="I416" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J416" s="3" t="str">
@@ -13365,7 +13368,7 @@
         <v/>
       </c>
       <c r="K416" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13382,7 +13385,7 @@
         <v>0</v>
       </c>
       <c r="I417" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J417" s="3" t="str">
@@ -13390,7 +13393,7 @@
         <v/>
       </c>
       <c r="K417" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13407,7 +13410,7 @@
         <v>0</v>
       </c>
       <c r="I418" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J418" s="3" t="str">
@@ -13415,7 +13418,7 @@
         <v/>
       </c>
       <c r="K418" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13432,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="I419" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J419" s="3" t="str">
@@ -13440,7 +13443,7 @@
         <v/>
       </c>
       <c r="K419" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13457,7 +13460,7 @@
         <v>0</v>
       </c>
       <c r="I420" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J420" s="3" t="str">
@@ -13465,7 +13468,7 @@
         <v/>
       </c>
       <c r="K420" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13482,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="I421" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J421" s="3" t="str">
@@ -13490,7 +13493,7 @@
         <v/>
       </c>
       <c r="K421" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13507,7 +13510,7 @@
         <v>0</v>
       </c>
       <c r="I422" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J422" s="3" t="str">
@@ -13515,7 +13518,7 @@
         <v/>
       </c>
       <c r="K422" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13532,7 +13535,7 @@
         <v>0</v>
       </c>
       <c r="I423" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J423" s="3" t="str">
@@ -13540,7 +13543,7 @@
         <v/>
       </c>
       <c r="K423" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13557,7 +13560,7 @@
         <v>0</v>
       </c>
       <c r="I424" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J424" s="3" t="str">
@@ -13565,7 +13568,7 @@
         <v/>
       </c>
       <c r="K424" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13582,7 +13585,7 @@
         <v>0</v>
       </c>
       <c r="I425" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J425" s="3" t="str">
@@ -13590,7 +13593,7 @@
         <v/>
       </c>
       <c r="K425" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13607,7 +13610,7 @@
         <v>0</v>
       </c>
       <c r="I426" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J426" s="3" t="str">
@@ -13615,7 +13618,7 @@
         <v/>
       </c>
       <c r="K426" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13632,7 +13635,7 @@
         <v>0</v>
       </c>
       <c r="I427" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J427" s="3" t="str">
@@ -13640,7 +13643,7 @@
         <v/>
       </c>
       <c r="K427" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13657,7 +13660,7 @@
         <v>0</v>
       </c>
       <c r="I428" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J428" s="3" t="str">
@@ -13665,7 +13668,7 @@
         <v/>
       </c>
       <c r="K428" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13682,7 +13685,7 @@
         <v>0</v>
       </c>
       <c r="I429" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J429" s="3" t="str">
@@ -13690,7 +13693,7 @@
         <v/>
       </c>
       <c r="K429" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13707,7 +13710,7 @@
         <v>0</v>
       </c>
       <c r="I430" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J430" s="3" t="str">
@@ -13715,7 +13718,7 @@
         <v/>
       </c>
       <c r="K430" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13732,7 +13735,7 @@
         <v>0</v>
       </c>
       <c r="I431" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J431" s="3" t="str">
@@ -13740,7 +13743,7 @@
         <v/>
       </c>
       <c r="K431" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13757,7 +13760,7 @@
         <v>0</v>
       </c>
       <c r="I432" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J432" s="3" t="str">
@@ -13765,7 +13768,7 @@
         <v/>
       </c>
       <c r="K432" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13782,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="I433" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J433" s="3" t="str">
@@ -13790,7 +13793,7 @@
         <v/>
       </c>
       <c r="K433" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13807,7 +13810,7 @@
         <v>0</v>
       </c>
       <c r="I434" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J434" s="3" t="str">
@@ -13815,7 +13818,7 @@
         <v/>
       </c>
       <c r="K434" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13832,7 +13835,7 @@
         <v>0</v>
       </c>
       <c r="I435" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J435" s="3" t="str">
@@ -13840,7 +13843,7 @@
         <v/>
       </c>
       <c r="K435" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13857,7 +13860,7 @@
         <v>0</v>
       </c>
       <c r="I436" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J436" s="3" t="str">
@@ -13865,7 +13868,7 @@
         <v/>
       </c>
       <c r="K436" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13882,7 +13885,7 @@
         <v>0</v>
       </c>
       <c r="I437" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J437" s="3" t="str">
@@ -13890,7 +13893,7 @@
         <v/>
       </c>
       <c r="K437" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13907,7 +13910,7 @@
         <v>0</v>
       </c>
       <c r="I438" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J438" s="3" t="str">
@@ -13915,7 +13918,7 @@
         <v/>
       </c>
       <c r="K438" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13932,7 +13935,7 @@
         <v>0</v>
       </c>
       <c r="I439" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J439" s="3" t="str">
@@ -13940,7 +13943,7 @@
         <v/>
       </c>
       <c r="K439" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13957,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="I440" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J440" s="3" t="str">
@@ -13965,7 +13968,7 @@
         <v/>
       </c>
       <c r="K440" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13982,7 +13985,7 @@
         <v>0</v>
       </c>
       <c r="I441" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J441" s="3" t="str">
@@ -13990,7 +13993,7 @@
         <v/>
       </c>
       <c r="K441" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -14007,7 +14010,7 @@
         <v>0</v>
       </c>
       <c r="I442" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J442" s="3" t="str">
@@ -14015,7 +14018,7 @@
         <v/>
       </c>
       <c r="K442" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -14032,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="I443" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J443" s="3" t="str">
@@ -14040,7 +14043,7 @@
         <v/>
       </c>
       <c r="K443" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -14057,7 +14060,7 @@
         <v>0</v>
       </c>
       <c r="I444" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J444" s="3" t="str">
@@ -14065,7 +14068,7 @@
         <v/>
       </c>
       <c r="K444" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -14082,7 +14085,7 @@
         <v>0</v>
       </c>
       <c r="I445" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J445" s="3" t="str">
@@ -14090,7 +14093,7 @@
         <v/>
       </c>
       <c r="K445" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -14107,7 +14110,7 @@
         <v>0</v>
       </c>
       <c r="I446" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J446" s="3" t="str">
@@ -14115,7 +14118,7 @@
         <v/>
       </c>
       <c r="K446" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -14132,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="I447" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J447" s="3" t="str">
@@ -14140,7 +14143,7 @@
         <v/>
       </c>
       <c r="K447" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -14157,7 +14160,7 @@
         <v>0</v>
       </c>
       <c r="I448" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J448" s="3" t="str">
@@ -14165,7 +14168,7 @@
         <v/>
       </c>
       <c r="K448" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -14182,7 +14185,7 @@
         <v>0</v>
       </c>
       <c r="I449" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J449" s="3" t="str">
@@ -14190,7 +14193,7 @@
         <v/>
       </c>
       <c r="K449" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -14207,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="I450" s="3">
-        <f t="shared" ref="I450:I501" si="30">IF(OR(G450="",G450=0),0,ROUND(IF(G450&lt;=30,50,IF(G450&gt;=60,1,50-((G450-30)*(50/30)))),2))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J450" s="3" t="str">
@@ -14215,7 +14218,7 @@
         <v/>
       </c>
       <c r="K450" s="4" t="str">
-        <f t="shared" ref="K450:K501" si="31">IF(J450="","",1+COUNTIFS($A$2:$A$501,A450,$B$2:$B$501,B450,$J$2:$J$501,"&gt;"&amp;J450))</f>
+        <f t="shared" ref="K450:K501" si="30">IF(J450="","",1+COUNTIFS($A$2:$A$501,A450,$B$2:$B$501,B450,$J$2:$J$501,"&gt;"&amp;J450))</f>
         <v/>
       </c>
     </row>
@@ -14232,7 +14235,7 @@
         <v>0</v>
       </c>
       <c r="I451" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="I451:I501" si="31">IF(OR(G451="",G451=0),0,IF(G451&lt;=40,50,IF(G451&gt;=61,0,ROUND(50-((G451-40)*(49/20)),2))))</f>
         <v>0</v>
       </c>
       <c r="J451" s="3" t="str">
@@ -14240,7 +14243,7 @@
         <v/>
       </c>
       <c r="K451" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14257,7 +14260,7 @@
         <v>0</v>
       </c>
       <c r="I452" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J452" s="3" t="str">
@@ -14265,7 +14268,7 @@
         <v/>
       </c>
       <c r="K452" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14282,7 +14285,7 @@
         <v>0</v>
       </c>
       <c r="I453" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J453" s="3" t="str">
@@ -14290,7 +14293,7 @@
         <v/>
       </c>
       <c r="K453" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14307,7 +14310,7 @@
         <v>0</v>
       </c>
       <c r="I454" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J454" s="3" t="str">
@@ -14315,7 +14318,7 @@
         <v/>
       </c>
       <c r="K454" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14332,7 +14335,7 @@
         <v>0</v>
       </c>
       <c r="I455" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J455" s="3" t="str">
@@ -14340,7 +14343,7 @@
         <v/>
       </c>
       <c r="K455" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14357,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="I456" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J456" s="3" t="str">
@@ -14365,7 +14368,7 @@
         <v/>
       </c>
       <c r="K456" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14382,7 +14385,7 @@
         <v>0</v>
       </c>
       <c r="I457" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J457" s="3" t="str">
@@ -14390,7 +14393,7 @@
         <v/>
       </c>
       <c r="K457" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14407,7 +14410,7 @@
         <v>0</v>
       </c>
       <c r="I458" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J458" s="3" t="str">
@@ -14415,7 +14418,7 @@
         <v/>
       </c>
       <c r="K458" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14432,7 +14435,7 @@
         <v>0</v>
       </c>
       <c r="I459" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J459" s="3" t="str">
@@ -14440,7 +14443,7 @@
         <v/>
       </c>
       <c r="K459" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14457,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="I460" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J460" s="3" t="str">
@@ -14465,7 +14468,7 @@
         <v/>
       </c>
       <c r="K460" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14482,7 +14485,7 @@
         <v>0</v>
       </c>
       <c r="I461" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J461" s="3" t="str">
@@ -14490,7 +14493,7 @@
         <v/>
       </c>
       <c r="K461" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14507,7 +14510,7 @@
         <v>0</v>
       </c>
       <c r="I462" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J462" s="3" t="str">
@@ -14515,7 +14518,7 @@
         <v/>
       </c>
       <c r="K462" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14532,7 +14535,7 @@
         <v>0</v>
       </c>
       <c r="I463" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J463" s="3" t="str">
@@ -14540,7 +14543,7 @@
         <v/>
       </c>
       <c r="K463" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14557,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="I464" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J464" s="3" t="str">
@@ -14565,7 +14568,7 @@
         <v/>
       </c>
       <c r="K464" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14582,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="I465" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J465" s="3" t="str">
@@ -14590,7 +14593,7 @@
         <v/>
       </c>
       <c r="K465" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14607,7 +14610,7 @@
         <v>0</v>
       </c>
       <c r="I466" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J466" s="3" t="str">
@@ -14615,7 +14618,7 @@
         <v/>
       </c>
       <c r="K466" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14632,7 +14635,7 @@
         <v>0</v>
       </c>
       <c r="I467" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J467" s="3" t="str">
@@ -14640,7 +14643,7 @@
         <v/>
       </c>
       <c r="K467" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14657,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="I468" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J468" s="3" t="str">
@@ -14665,7 +14668,7 @@
         <v/>
       </c>
       <c r="K468" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14682,7 +14685,7 @@
         <v>0</v>
       </c>
       <c r="I469" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J469" s="3" t="str">
@@ -14690,7 +14693,7 @@
         <v/>
       </c>
       <c r="K469" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14707,7 +14710,7 @@
         <v>0</v>
       </c>
       <c r="I470" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J470" s="3" t="str">
@@ -14715,7 +14718,7 @@
         <v/>
       </c>
       <c r="K470" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14732,7 +14735,7 @@
         <v>0</v>
       </c>
       <c r="I471" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J471" s="3" t="str">
@@ -14740,7 +14743,7 @@
         <v/>
       </c>
       <c r="K471" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14757,7 +14760,7 @@
         <v>0</v>
       </c>
       <c r="I472" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J472" s="3" t="str">
@@ -14765,7 +14768,7 @@
         <v/>
       </c>
       <c r="K472" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14782,7 +14785,7 @@
         <v>0</v>
       </c>
       <c r="I473" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J473" s="3" t="str">
@@ -14790,7 +14793,7 @@
         <v/>
       </c>
       <c r="K473" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14807,7 +14810,7 @@
         <v>0</v>
       </c>
       <c r="I474" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J474" s="3" t="str">
@@ -14815,7 +14818,7 @@
         <v/>
       </c>
       <c r="K474" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14832,7 +14835,7 @@
         <v>0</v>
       </c>
       <c r="I475" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J475" s="3" t="str">
@@ -14840,7 +14843,7 @@
         <v/>
       </c>
       <c r="K475" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14857,7 +14860,7 @@
         <v>0</v>
       </c>
       <c r="I476" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J476" s="3" t="str">
@@ -14865,7 +14868,7 @@
         <v/>
       </c>
       <c r="K476" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14882,7 +14885,7 @@
         <v>0</v>
       </c>
       <c r="I477" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J477" s="3" t="str">
@@ -14890,7 +14893,7 @@
         <v/>
       </c>
       <c r="K477" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14907,7 +14910,7 @@
         <v>0</v>
       </c>
       <c r="I478" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J478" s="3" t="str">
@@ -14915,7 +14918,7 @@
         <v/>
       </c>
       <c r="K478" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14932,7 +14935,7 @@
         <v>0</v>
       </c>
       <c r="I479" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J479" s="3" t="str">
@@ -14940,7 +14943,7 @@
         <v/>
       </c>
       <c r="K479" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14957,7 +14960,7 @@
         <v>0</v>
       </c>
       <c r="I480" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J480" s="3" t="str">
@@ -14965,7 +14968,7 @@
         <v/>
       </c>
       <c r="K480" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -14982,7 +14985,7 @@
         <v>0</v>
       </c>
       <c r="I481" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J481" s="3" t="str">
@@ -14990,7 +14993,7 @@
         <v/>
       </c>
       <c r="K481" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15007,7 +15010,7 @@
         <v>0</v>
       </c>
       <c r="I482" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J482" s="3" t="str">
@@ -15015,7 +15018,7 @@
         <v/>
       </c>
       <c r="K482" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15032,7 +15035,7 @@
         <v>0</v>
       </c>
       <c r="I483" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J483" s="3" t="str">
@@ -15040,7 +15043,7 @@
         <v/>
       </c>
       <c r="K483" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15057,7 +15060,7 @@
         <v>0</v>
       </c>
       <c r="I484" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J484" s="3" t="str">
@@ -15065,7 +15068,7 @@
         <v/>
       </c>
       <c r="K484" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15082,7 +15085,7 @@
         <v>0</v>
       </c>
       <c r="I485" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J485" s="3" t="str">
@@ -15090,7 +15093,7 @@
         <v/>
       </c>
       <c r="K485" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15107,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="I486" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J486" s="3" t="str">
@@ -15115,7 +15118,7 @@
         <v/>
       </c>
       <c r="K486" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15132,7 +15135,7 @@
         <v>0</v>
       </c>
       <c r="I487" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J487" s="3" t="str">
@@ -15140,7 +15143,7 @@
         <v/>
       </c>
       <c r="K487" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15157,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="I488" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J488" s="3" t="str">
@@ -15165,7 +15168,7 @@
         <v/>
       </c>
       <c r="K488" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15182,7 +15185,7 @@
         <v>0</v>
       </c>
       <c r="I489" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J489" s="3" t="str">
@@ -15190,7 +15193,7 @@
         <v/>
       </c>
       <c r="K489" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15207,7 +15210,7 @@
         <v>0</v>
       </c>
       <c r="I490" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J490" s="3" t="str">
@@ -15215,7 +15218,7 @@
         <v/>
       </c>
       <c r="K490" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15232,7 +15235,7 @@
         <v>0</v>
       </c>
       <c r="I491" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J491" s="3" t="str">
@@ -15240,7 +15243,7 @@
         <v/>
       </c>
       <c r="K491" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15257,7 +15260,7 @@
         <v>0</v>
       </c>
       <c r="I492" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J492" s="3" t="str">
@@ -15265,7 +15268,7 @@
         <v/>
       </c>
       <c r="K492" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15282,7 +15285,7 @@
         <v>0</v>
       </c>
       <c r="I493" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J493" s="3" t="str">
@@ -15290,7 +15293,7 @@
         <v/>
       </c>
       <c r="K493" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15307,7 +15310,7 @@
         <v>0</v>
       </c>
       <c r="I494" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J494" s="3" t="str">
@@ -15315,7 +15318,7 @@
         <v/>
       </c>
       <c r="K494" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15332,7 +15335,7 @@
         <v>0</v>
       </c>
       <c r="I495" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J495" s="3" t="str">
@@ -15340,7 +15343,7 @@
         <v/>
       </c>
       <c r="K495" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15357,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="I496" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J496" s="3" t="str">
@@ -15365,7 +15368,7 @@
         <v/>
       </c>
       <c r="K496" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15382,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="I497" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J497" s="3" t="str">
@@ -15390,7 +15393,7 @@
         <v/>
       </c>
       <c r="K497" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15407,7 +15410,7 @@
         <v>0</v>
       </c>
       <c r="I498" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J498" s="3" t="str">
@@ -15415,7 +15418,7 @@
         <v/>
       </c>
       <c r="K498" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15432,7 +15435,7 @@
         <v>0</v>
       </c>
       <c r="I499" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J499" s="3" t="str">
@@ -15440,7 +15443,7 @@
         <v/>
       </c>
       <c r="K499" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15457,7 +15460,7 @@
         <v>0</v>
       </c>
       <c r="I500" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J500" s="3" t="str">
@@ -15465,7 +15468,7 @@
         <v/>
       </c>
       <c r="K500" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -15482,7 +15485,7 @@
         <v>0</v>
       </c>
       <c r="I501" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="J501" s="3" t="str">
@@ -15490,7 +15493,7 @@
         <v/>
       </c>
       <c r="K501" s="4" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
